--- a/Final_Evaluation_Report_Fixed (1).xlsx
+++ b/Final_Evaluation_Report_Fixed (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engma\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFA748B-D6C3-4B63-9061-609FC9D2BD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939009B5-2DEF-492F-888D-C7C68C67649B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="158">
   <si>
     <t>Date</t>
   </si>
@@ -71,10 +71,10 @@
     <t>verdict</t>
   </si>
   <si>
-    <t>2026-01-26 06:26:32</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvXoVAbEEo+sMU3MUDSAwv_kPH3++80jumfWkDRev9nxQ@mail.gmail.com&gt;</t>
+    <t>2026-01-28 16:35:12</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnvo2gRhdtWu-K2q7tieZZc3ZkeBs20mLV6sR=Kr2RmEuw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>xmio.511x@gmail.com</t>
@@ -84,7 +84,7 @@
   </si>
   <si>
     <t xml:space="preserve">*نفيد سعادتكم تعطل وحدات تكييف الاسبلت في الدور الثاني بمبنى مركز شرطة
-العريجاء، حيث تسبب العطل في  ارتفاع ملحوظ في درجات الحرارة داخل المكاتب
+العريجاء، حيث تسبب العطل في ارتفاع ملحوظ في درجات الحرارة داخل المكاتب
 الإدارية وأثر سلباً على سير العمل وبيئة الموظفين**.*
 *عليه، نأمل من سعادتكم التوجيه لمن يلزم بسرعة وقوف الفرق الفنية المختصة على
 الموقع، وإجراء الصيانة اللازمة وإصلاح العطل بصفة عاجلة لضمان استمرارية
@@ -95,38 +95,54 @@
 </t>
   </si>
   <si>
-    <t>**الموضوع:** رد على البلاغ حول تعطل وحدات التكييف في دور ثاني مركز شرطة العريجاء  
-السيد العقيد / محمد  
-مدير مركز شرطة العريجاء  
-تحية طيبة وبعد،
-نود أن نشكركم على تواصلكم السريع والتقرير المقدم حول تعطل وحدات التكييف من نوع الأسبلت في الدور الثاني بمبنى مركز الشرطة، والذي تسبب في ارتفاع درجات الحرارة داخل المكاتب الإدارية وأثر سلبًا على البيئة العملية.
-بناءً على ما ورد في البلاغ، فإننا نؤكد على وجوب معالجة هذا العطل فورًا، وفقًا للإجراءات المنصوص عليها في **الفقرة 65 من الشروط والمواصفات الفنية** المتعلقة بأعمال الصيانة الطارئة، وخاصة البند **7-3-ب**، والذي يُلزم المقاول بتوفير الفنيين فور تلقي البلاغ وإجراء الصيانة اللازمة.
-لذلك:
-1. تم التواصل فوريًا مع **شركة واحة صقر لعربيّة للتجارة والمقاولات**، وهي الشركة المنفذة لخدمات الصيانة والتشغيل بموجب **العقد الخاص بمركز شرطة العريجاء** تحت مشروع "صيانة وتشغيل المواقع الأمنية بمنطقة الرياض (المرحلة الثالثة)".
-2. تم توجيه الشركة بإرسال فريق فني مؤهل إلى الموقع فورًا لإجراء الفحص والصيانة الضرورية، وتحديد سبب العطل وتقديم تقرير فني مفصل حوله.
-3. في حال استدعى الأمر استخدام قطع غيار، ستتحمل الشركة المسؤولية الكاملة وفقًا للبنود التعاقدية، وفي حال تأخر التنفيذ، سيتم تطبيق الغرامات وفقًا للفقرة **3-1/1 و3-1/3**، والتي تتراوح بين 500 ريال يوميًا حسب مدة التأخير وعدم الالتزام بالجدولة الزمنية.
-4. سنقوم بمتابعة تنفيذ الإصلاح عن كثب، وسيتم إعلامكم فور انتهاء العمل وعودته إلى وضعه الطبيعي.
-نؤكد لكم أننا نعطي أولوية كاملة لمعالجة مثل هذه الحالات التي تؤثر على سير العمل وبيئة الموظفين، وسنحرص على تفعيل البنود القانونية والفنية المعتمدة في العقود لتوفير أفضل مستويات الخدمة.
+    <t>السيد / مدير شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد:  
+"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
+السلام عليكم ورحمة الله وبركاته،،،  
+نُخطركم علمًا بوجود عطل طارئ في وحدات تكييف الأسبلت في الدور الثاني بمبنى مركز شرطة العريجاء، وقد تسبب ذلك في ارتفاع ملحوظ في درجات الحرارة داخل المكاتب الإدارية، مما أدى إلى تأثير سلبي واضح على بيئة العمل وسير العمليات الإدارية.  
+بناءً على ما ورد إلينا، فإننا نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخّر في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين.  
+ونلفت انتباهكم إلى وجوب الحرص على تنفيذ الأعمال بصدد الجدول الزمني المحدد، والتزام الشركة بكافة الشروط التعاقدية المتعلقة بتوفير الخدمة الفورية في حال حدوث أعطال طارئة.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة / شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة) السلام عليكم ورحمة الله وبركاته،،،  نُخطركم علمًا بوجود عطل طارئ في **وحدات تكييف الأسبلت في الدور الثاني بمبنى مركز شرطة العريجاء**، وقد تسبب ذلك في **ارتفاع ملحوظ في درجات الحرارة داخل المكاتب الإدارية**، مما أدى إلى **تأثير سلبي واضح على بيئة العمل وسير العمليات الإدارية**.  بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخر في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين. نلفت انتباهكم إلى **الفقرة 3-1/1** من الشروط والمواصفات الفنية، والتي تنص على فرض **غرامة قدرها 500 ريال يوميًا** عن كل جهاز أو نظام يظل العطل فيه قائماً، خاصة إذا كان ذلك يؤثر على ظروف العمل المحيطية. كذلك، نذكركم بأنه في حال تم إبلاغكم عن العطل ولم تتدخلوا إلا بعد مضي **أكثر من 12 ساعة**، فإنه سيتم **فرض الغرامة كاملة دون خصم**، ولن يُنظر إلى أي ذريعة أو تبرير. نؤكد لكم أن أي تأخير أو إهمال في التعامل مع هذا العطل سيكون له آثار قانونية ومالية مباشرة على عقدكم، وسيتم اتخاذ الإجراءات المناسبة وفقًا للبنود التعاقدية. وتقبلوا تحياتي،، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة تغطي الإجراءات الأساسية (التواصل مع الشركة، توجيه الفريق الفني، تطبيق الغرامات) لكنها تفتقر إلى الحدة القانونية الواضحة في التهديد بالغرامات وفق الفقرة 3-1/1 كما في الرد النموذجي. الرد النموذجي يُبرز التأثير السلبي على البيئة العمل بشكل أوضح ويستخدم بنود العقد بشكل أكثر تفصيلًا.</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على خطأ إملائي في اسم الشركة (عربيّة بدلًا من عروبة) وتجريء غير ضروري في بعض الأماكن (مثل 'عربيّة'). الرد النموذجي أكثر انتظامًا في الأسلوب الرسمي ويعتمد على ترقيم الفقرات بشكل أكثر دقة.</t>
+    <t xml:space="preserve">السادة / شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد: عملية
+صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض
+(المرحلة الثالثة)
+السلام عليكم ورحمة الله وبركاته،،،
+نُخطركم علمًا بوجود عطل طارئ في وحدات تكييف الأسبلت في الدور الثاني
+بمبنى مركز شرطة العريجاء وقد تسبب ذلك في ارتفاع ملحوظ في درجات الحرارة
+داخل المكاتب الإدارية مما أدى إلى تأثير سلبي واضح على بيئة العمل وسير
+العمليات الإدارية.
+بناءً على ما ورد إلينا، فإننا نؤكد لكم أنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخر في التعامل
+مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وبيئة الموظفين.
+نلفت انتباهكم إلى الفقرة 3-1/1 من الشروط والمواصفات الفنية، والتي تنص
+على فرض غرامة قدرها 500 ريال يوميًا عن كل جهاز أو نظام يظل العطل فيه
+قائماً، خاصة إذا كان ذلك يؤثر على ظروف العمل المحيطية.
+كذلك، نذكركم بأنه في حال تم إبلاغكم عن العطل ولم تتدخلوا إلا بعد مضي
+أكثر من 12 ساعة، فإنه سيتم فرض الغرامة كاملة دون خصم، ولن يُنظر إلى أي
+ذريعة أو تبرير.
+نؤكد لكم أن أي تأخير أو إهمال في التعامل مع هذا العطل سيكون له آثار
+قانونية ومالية مباشرة على عقدكم، وسيتم اتخاذ الإجراءات المناسبة وفقًا
+للبنود التعاقدية.
+وتقبلوا تحياتي،،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تفتقر إلى الإشارة إلى البنود التعاقدية المحددة (مثل الفقرة 3-1/1) وغرامات التأخير (500 ريال يوميًا) المذكورة في الرد النموذجي. كما أن التحذير من العواقب القانونية والمالية غير واضح في مسودة البوت، مما يقلل من قوة الرسالة الإدارية.</t>
+  </si>
+  <si>
+    <t>وجود فاصلة زائدة بعد 'الله وبركاته،،،'، وخطأ إملائي في 'التأخّر' (يجب أن يكون 'التأخر'). كما أن توزيع الجمل الطويلة في مسودة البوت أقل وضوحًا مقارنة بالرد النموذجي الذي قسم النص إلى فقرات قصيرة لتحسين القراءة.</t>
   </si>
   <si>
     <t>يحتاج تعديل</t>
   </si>
   <si>
-    <t>2026-01-26 06:28:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntdtozC8BBGjK5ZATBHWr4vt=kZuS+t94Y-a35WuD1-7w@mail.gmail.com&gt;</t>
+    <t>2026-01-28 16:37:34</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuVGJkwE7iJ7nDbhtq=jOmPbVs=7zzeUqOCs5TRzno34w@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">نفيد سعادتكم بتعطل بعض وحدات الانارة في قاعة الاجتماعات بالمبنى طرفنا حيث
@@ -139,30 +155,57 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير الصيانة  
-شركة صقور العرب للمقاولات العامة  
-السلام عليكم ورحمة الله وبركاته  
-إشارة إلى بلاغ مقدم من مدير مركز شرطة الملز حول **تعطل بعض وحدات الإضاءة في قاعة الاجتماعات بالمبنى**، وهو ما يؤثر مباشرةً على سير العمليات الإدارية والاجتماعات اليومية التي تعقد في تلك القاعة، فقد تم توجيه إنذار رسمي إليكم بشأن هذا الشأن.
-بناءً على البنود التعاقدية وخاصة **الفقرة 65 من العقد** المتعلقة بمسؤوليات المقاول في **الصيانة الطارئة والعاجلة**، فإننا **نقترح بقوة** أن تقوموا فورًا بإرسال فريق فني مؤهل إلى الموقع لإجراء الصيانة الضرورية وإصلاح وحدات الإضاءة المعطّلة، وذلك ضمن **التوقيت المحدد (12 ساعة)** من تاريخ تسلم هذا البلاغ.
-كما نلفت انتباهكم إلى أن **التقصير في الوفاء بالتزامات العقد قد يؤدي إلى تطبيق الغرامات المالية بمعدل 500 ريال سعودي يوميًا**، وفقًا للبنود التعاقدية المتفق عليها.
-ونؤكد على ضرورة **إشعارنا بكافة الإجراءات المتخذة والتقارير الفنية** فور انتهاء الصيانة، بهدف متابعتها وتوثيقها.
+    <t>السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية)  
+السلام عليكم ورحمة الله وبركاته،،،  
+نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات بمبنى مركز شرطة الملز**، وهو أمر مستجد رغم وجود بلاغ سابق تم رفعه حول ذات الموضوع، إلا أن الشركة لم تستجب له بشكل فعال، مما أدى إلى تفاقم الوضع وتأثيره السلبي على سير العمل الرسمي.  
+بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التسويف أو تقديم أي ذريعة تؤخر تنفيذ الخدمة، لما لذلك من تأثير مباشر على استخدام القاعة لاجتماعات هامة تتعلق بسير الأعمال الإدارية والأمنية.  
+نلفت انتباهكم إلى الفقرتين **(١٢-أ)** و**(٣٥-ب)** من العقد الموقع بين الطرفين، اللواتي تحددان التزام الشركة بتقديم خدمات الصيانة الطارئة في الوقت المناسب، وفي حال حدوث أي تأخير بدون مبرر مشروع، سيتم تطبيق الغرامات اليومية وفقًا للبنود النظامية، ولن يُنظر لأي اعتذار أو تبرير.  
+كما نُعيد التنويه بأن أي تقصير في الالتزام بالوقت أو الجودة قد يؤدي إلى **تطبيق آثار قانونية مباشرة**، بما فيها إنهاء العلاقة التعاقدية إذا دعت الحاجة.  
+**ننتظر تأكيدكم على توفر الفريق الفني في الموقع خلال ساعة واحدة من تاريخ استلام هذا الإشعار**، وإلا سنقوم بإتخاذ الإجراءات النظامية الفورية.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية) السلام عليكم ورحمة الله وبركاته،،، نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات بمبنى مركز شرطة الملز**، وهو أمر يستدعي تدخلًا فوريًا، خاصة وأن تلك القاعة تستخدم بشكل يومي لإجراء الاجتماعات الهامة، ولا يمكن التسامح مع هذا التقصير الذي يؤثر سلبًا على سير العمل واستخدام المنشآت الأساسية. بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على أداء العمل وفعالية التواصل التنظيمي. نلفت انتباهكم إلى **الفقرة 65 من اللائحة المتعلقة بالتشغيل والصيانة للأعمال الكهربائية**، والتي توجب على المقاول القيام باستبدال القطع أو الأجزاء أو الأجهزة التالفة أو المحترقة وتأمين ما يلزم من الوقود والزيوت والشحومات وخلافه، وفقًا للأصول الفنية المتبعة وتعليمات الشركات الصانعة. كذلك، نذكركم بأنه **مقتضب الفقرة (ب) ضمن نفس الفقرة 65**، أن على المقاول تنسيق سجلات إجراءات الصيانة على هيئة نظام للجداول البيانية الجدارية، والسماح بالتخطيط المستقبلي لتلبية الاحتياجات المهنية، وهو ما لم يتم الالتزام به أيضًا في هذا الملف. نحذركم بشدة من التكرار أو التباطؤ في المستقبل، إذ سيعرضكم ذلك إلى الغرامات المالية والتقارير الرسمية أمام الجهات المختصة**. وتقبلوا تحياتي،، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة تغطي النقاط الأساسية (الإبلاغ عن العطل، الإشارة إلى الفقرة 65، تحديد المهلة الزمنية، التحذير من الغرامات)، لكنها تفتقر إلى التفاصيل الدقيقة مثل الإشارة إلى 'الفقرة (ب) ضمن الفقرة 65' وضرورة إعداد 'سجلات إجراءات الصيانة' كما في الرد النموذجي. كما أن لغة التحذير أقل حدة في المسودة.</t>
-  </si>
-  <si>
-    <t>المسودة تستخدم بناءً لغويًا صحيحًا، لكنها تفتقر إلى التنسيق الكامل بين الجمل (مثل استخدام الفواصل والعبارات الربطية). الرد النموذجي أكثر اتساقًا في استخدام العلامات الترقيمية (كالفاصلة المنقوطة) ويرتبط الجمل بعبارات رسمية مثل 'بناءً على ما ورد إلينا' و'نلفت انتباهكم إلى'.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:31:13</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnv2DOABih+ucqu44JzpoxOSQfh8k8RuvjqM7P_0YAJ5aA@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة
+ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض
+(المرحلة الثانية)
+السلام عليكم ورحمة الله وبركاته،،،
+نُخطركم علمًا بوجود عطل طارئ في **بعض وحدات الإضاءة في قاعة الاجتماعات
+بمبنى مركز شرطة الملز**، وهو أمر مستجد رغم وجود بلاغ سابق تم رفعه حول
+ذات الموضوع، إلا أن الشركة لم تستجب له بشكل فعال، مما أدى إلى تفاقم
+الوضع وتأثيره السلبي على سير العمل الرسمي.
+بناءً على ما ورد إلينا، فإننا **نؤكد لكم أنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التسويف أو
+تقديم أي ذريعة تؤخر تنفيذ الخدمة، لما لذلك من تأثير مباشر على استخدام
+القاعة لاجتماعات هامة تتعلق بسير الأعمال الإدارية والأمنية.
+نلفت انتباهكم إلى الفقرتين **(١٢-أ)** و**(٣٥-ب)** من العقد الموقع بين
+الطرفين، اللواتي تحددان التزام الشركة بتقديم خدمات الصيانة الطارئة في
+الوقت المناسب، وفي حال حدوث أي تأخير بدون مبرر مشروع، سيتم تطبيق
+الغرامات اليومية وفقًا للبنود النظامية، ولن يُنظر لأي اعتذار أو تبرير.
+كما نُعيد التنويه بأن أي تقصير في الالتزام بالوقت أو الجودة قد يؤدي
+إلى **تطبيق آثار قانونية مباشرة**، بما فيها إنهاء العلاقة التعاقدية
+إذا دعت الحاجة.
+**ننتظر تأكيدكم على توفر الفريق الفني في الموقع خلال ساعة واحدة من
+تاريخ استلام هذا الإشعار**، وإلا سنقوم بإتخاذ الإجراءات النظامية
+الفورية.
+وتقبلو تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تغطي جميع النقاط الجوهرية من الرد النموذجي (الإبلاغ عن العطل، الإشارة للبنود العقدية، تحديد المهلة الزمنية). الفرق الوحيد هو تكثيف بعض الجمل (مثل دمج جملة الفقرات العقدية) دون إهمال أي معلومات حاسمة.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية أو نحوية. استخدام 'اللواتي' صحيح ل-reference إلى الفقرات (مفردة جمع مؤنث سالم). الفواصل والنقاط موزعة بشكل منسق. الثلاث فواصل بعد التحيات هي خيار أسلوبي وليس خطأ.</t>
+  </si>
+  <si>
+    <t>ناجح</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:39:29</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwns_QcDGst0z9XJNzJveNrm56yeiNfe46DtP-rZ7KkTdsw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">نفيد سعادتكم بوجود تسريبات مياه في الدور الأرضي مما تسبب في توقف خدمة
@@ -174,34 +217,42 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة صقور العرب للمقاولات العامة  
-المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية)
-السلام عليكم ورحمة الله وبركاته،،،  
-نُخطركم علمًا بوجود **تسريبات مياه في الدور الأرضي بمبنى مركز شرطة الملز**، وقد أدت هذه التسريبات إلى **توقف جزئي لخدمة المياه**، بالإضافة إلى **هدر كبير في المياه**، مما يعكس تقصيرًا في أداء الخدمات التعاقدية المتفق عليها.
-بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سير العمليات الإدارية والخدمات الأساسية.
-نلفت انتباهكم إلى **الفقرة 65 – 1/7 من اللائحة الخاصة بالصيانة الكهربائية والميكانيكية**، والتي تنص على ضرورة **معالجة حالات التسرب فورًا**، وضرورة **إبلاغ الجهات المعنية فور ظهور أي تسرب أو انسداد** بهدف اتخاذ الإجراءات الفورية.
-كذلك، نشير إلى أن **التقاعس في التنفيذ أو التأخير في إنجاز الصيانة يعتبر مخالفًا لبنود العقد**، وبالتالي سيتم **تطبيق الغرامات المالية بموجب البندين 65 و3-1/1 من العقد**، وذلك بمعدل **500 ريال سعودي يوميًا** في حالة التأخير دون مسوّغ مشروع.
-رجاءً تفضلوا بالإبلاغ عن اسم الفريق الفني الذي سيقوم بالزيارة، وعن توقيت الوصول المتوقع، وتفاصيل الإصلاح المقترحة.
+    <t>السادة / شركة صقور العرب للمقاولات العامة المنفذة للعقد: عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثانية)
+السلام عليكم ورحمة الله وبركاته:
+بناءً على البلاغ الوارد من مركز شرطة الملز، فإن هناك تسريبات مياه في الدور الأرضي أدت إلى توقف جزئي لخدمة المياه وهدر في كميات كبيرة من المياه. ونظرًا لخطورة هذا العطل وتأثيره السلبي على الخدمات الأساسية، **نشدد على ضرورة توجيه فريق فني فوري إلى الموقع لفحص وتحديد مواقع التسريب وإجراء الصيانة والإصلاح العاجل دون أي تأخير**، طبقًا للفقرة 65 أ-10 من الشروط التعاقدية المتعلقة بأعمال الفواصل والعزل لتسرب المياه، والتي تنص على معالجة التسريبات فور ظهورها.
+إن أي تأخير في التنفيذ لا يُنظر فيه بأي ذريعة، ويُعد انتهاكًا واضحًا لبندي العقد رقم (12/أ) والمتعلق بالالتزام بالوقت، ورقم (15/ب) الخاص بالخدمة الفورية في الحالات الطارئة، مما قد يؤدي إلى تطبيق الغرامات اليومية بمجرد بدء التأخير، بالإضافة إلى الآثار القانونية المباشرة التي ستتخذها الجهات المعنية.
+**إذًا، يجب عليكم التحرك فورًا، وليس هناك مجال للتلكؤ أو التسويف تحت أي ظرف كان.**
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة شركة صقور العرب للمقاولات العامة** السلام عليكم ورحمة الله وبركاته: بناءً على البلاغ الوارد من مركز شرطة الملز، فإن هناك تسريبات مياه في الدور الأرضي أدت إلى توقف جزئي لخدمة المياه وهدر في كميات كبيرة من المياه. ونظرًا لخطورة هذا العطل وتأثيره السلبي على الخدمات الأساسية، **نشدد على ضرورة توجيه فريق فني فوري إلى الموقع لفحص وتحديد مواقع التسريب وإجراء الصيانة والإصلاح العاجل دون أي تأخير**، طبقًا للفقرة 65 أ-10 من الشروط التعاقدية المتعلقة بأعمال الفواصل والعزل لتسرب المياه، والتي تنص على معالجة التسريبات فور ظهورها. كما نحذر من أن أي تأخير في تنفيذ الإصلاح سيعرض الشركة إلى تطبيق الغرامات وفق الأنظمة الناظمة للعقود. وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة تشمل تفاصيل إضافية مثل البنود القانونية (65 – 1/7) وغرامات محددة (500 ريال يوميًا)، مما يعزز وضوح الإجراءات. الرد النموذجي أقصر ويعتمد على بند مختلف (65 أ-10) دون تحديد مبلغ الغرامة.</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على فواصل زائدة (،،،) وتنسيق غير متسق (مثل **النص**)، بينما الرد النموذجي أكثر انتظامًا في الهيكل والعلامات الترفيهية.</t>
-  </si>
-  <si>
-    <t>ناجح</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:33:38</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvaC6LNNT8LtpJ_kbxvxueHYaKTDF4DW1tG56BSwVo=Lw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة / شركة صقور العرب للمقاولات العامة
+السلام عليكم ورحمة الله وبركاته:
+بناءً على البلاغ الوارد من مركز شرطة الملز، فإن هناك تسريبات مياه في
+الدور الأرضي أدت إلى توقف جزئي لخدمة المياه وهدر في كميات كبيرة من
+المياه.
+ونظرًا لخطورة هذا العطل وتأثيره السلبي على الخدمات الأساسية، نشدد على
+ضرورة توجيه فريق فني فوري إلى الموقع لفحص وتحديد مواقع التسريب وإجراء
+الصيانة والإصلاح العاجل دون أي تأخير، طبقًا للفقرة 65 أ-10 من الشروط
+التعاقدية المتعلقة بأعمال الفواصل والعزل لتسرب المياه، والتي تنص على
+معالجة التسريبات فور ظهورها.
+كما نحذر من أن أي تأخير في تنفيذ الإصلاح سيعرض الشركة إلى تطبيق
+الغرامات وفق الأحكام القانونية والتعاقدية المعمول بها.
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على تفاصيل إضافية غير ضرورية مثل أرقام العقود (12/أ و15/ب) وتهديدات قانونية مبالغ فيها. الرد النموذجي أكثر احترافية بتركيزه على التحذير من الغرامات دون تفصيل غير مطلوب. المسودة تستخدم لغة قوية (مثل 'ليس هناك مجال للتلكؤ') بينما الرد النموذجي أكثر توازنًا.</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على تكرار في ذكر 'التأخير' وعبارات غير مُصاغة بسلاسة مثل 'الآثار القانونية المباشرة التي ستتخذها الجهات المعنية'. الرد النموذجي أكثر نعومة في التعبير وتجنبت التعقيدات الزائدة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:42:35</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnsSLfRW+1KghTW5y4YjzgndTaubQsZhV+6EYwrvrFz_mQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">*نفيد سعادتكم، بتعطل مضخة الحريق* *في المستودع رقم (3)، حيث لوحظ انخفاض حاد
@@ -215,30 +266,50 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعرابة للتجارة والمقاولات المنفذة للعقد:  
-عملية صيانة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)
-السلام عليكم ورحمة الله وبركاته:
-نُخطركم علمًا بوجود **عطل طارئ في مضخة الحريق في المستودع رقم (3)**، حيث لوحظ **انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق**، مما أدى إلى **توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب**، ويشكل هذا العطل تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع.
-بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات اللوجستية والاحتياجات الأمنية.
-نلفت انتباهكم إلى **الفقرة 3-1/1 من الشروط التعاقدية**، والتي تنص على فرض غرامة قدرها **500 ريال يومياً** عن كل جهاز أو نظام يظل العطل قائماً فيه، وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة الحريق.
-**إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام القانونية والتعاقدية المعمول بها**.
+    <t>السيد / شركة صقور العرب للمقاولات العامة  
+السلام عليكم ورحمة الله وبركاته:  
+بناءً على البلاغ الوارد من مدير مستودعات الأمن الدبلوماسي، فقد تم تأكيد وجود عطل طارئ في مضخة الحريق في المستودع رقم (3)، والذي أدى إلى انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق، وبالتالي توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب، وهو ما يمثل تهديدًا مباشرًا لسلامة التجهيزات والمنشآت.  
+وبحسب الفقرة 65 أ-10 من الشروط التعاقدية، والتزامًا بما ورد في الفقرة 65 7-3-ب حول الصيانة الطارئة، فإنه **يجب** على الشركة توجيه فريق فني فوري إلى الموقع لفحص مضخة الحريق وإجراء الصيانة والإصلاح العاجل دون أي تأخير، وتحقيق استعادة النظام إلى حالته التشغيلية الكاملة.  
+كما نؤكد أنه **لا يُنظر لأي ذريعة** فيما يتعلق بتكرار مثل هذه الحالات، وأن أي تأخر في التنفيذ سيُعتبر مخالفًا لبنود العقد، وسيترتب عليه **تطبيق الغرامات وفق البندين 3-1/1 و3-1/2 من الفقرة 65**، اللذين يربطان بين التزام المقاول بالوقت والخدمة الفورية، ويمنحان حق فرض غرامات يومية مباشرة في حال التأخر.  
+وعلينا تحذير الشركة بأنه في حال تكرار مثل هذه الأعطال أو التأخير في الإصلاح، ستتخذ الإجراءات القانونية المناسبة، بما في ذلك **فرض الغرامات اليومية بمعدل 500 ريال يوميًا**، وقد تصل إلى إنهاء العقد في حال تكرار المخالفات.  
+ونحن إذ نوجهكم إلى تنفيذ الأوامر السابقة فورًا، فإننا ننتظر تقريرًا فنيًا مفصلاً عن سبب العطل والإجراءات المتخذة لإزالته، مع توثيق القطع المعيبة إن وُجدت.  
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد: عملية صيانة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة) السلام عليكم ورحمة الله وبركاته: نُخطركم علمًا بوجود عطل طارئ في مضخة الحريق في المستودع رقم (3)**، حيث لوحظ **انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق**، مما أدى إلى **توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب**، ويشكل هذا العطل تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع. بناءً على ما ورد إلينا، فإننا **نؤكد لكم بأنه يجب عليكم إرسال فريق فني فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل**، وعدم التأخير في التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات اللوجستية والاحتياجات الأمنية. نلفت انتباهكم إلى **الفقرة 3-1/1 من الشروط التعاقدية**، والتي تنص على فرض غرامة قدرها 500 ريال يومياً** عن كل جهاز أو نظام يظل العطل قائماً فيه، وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة الحريق. إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام القانونية والتعاقدية المعمول بها. وتقبلوا تحياتي  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على جميع العناصر الأساسية (الإخطار بالعطل، الإشارة للبنود التعاقدية، التهديد بالغرامات)، لكنها تفتقر إلى التنسيق الرسمي في توجيه الرسالة (مثل استخدام 'السادة' بدلاً من 'السيد / مدير')، ووجود فواصل غير متناسقة في توزيع المعلومات.</t>
-  </si>
-  <si>
-    <t>أخطاء في الأسلوب: 1) استخدام 'تقبلو' بدلاً من 'تقبلوا' في الإغلاق. 2) وجود علامات نجمية زائدة (**). 3) تكرار كلمة 'الشكل' في 'بالشكل المطلوب'. 4) غياب علامات الترقيم المناسبة في بعض الجمل.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:35:44</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnsh_0v0VwYRhdD3Srjuwga_Tc_hM5ioCEfCzPjuzERfZw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد: عملية صيانة
+وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة
+الثالثة)
+السلام عليكم ورحمة الله وبركاته:
+نُخطركم علمًا بوجود عطل طارئ في مضخة الحريق في المستودع رقم (3)، حيث
+لوحظ انخفاض حاد في ضغط شبكة المياه المخصصة لمكافحة الحريق، مما أدى إلى
+توقف نظام الإطفاء التلقائي عن العمل بالشكل المطلوب، ويشكل هذا العطل
+تهديداً حقيقياً لسلامة التجهيزات والبنية التحتية للمستودع.
+بناءً على ما ورد إلينا، فإننا نؤكد لكم بأنه يجب عليكم إرسال فريق فني
+فوري إلى الموقع لتقييم العطل وإصلاحه بشكل عاجل، وعدم التأخير في
+التعامل مع هذه المشكلة، لما لها من تأثير مباشر على سلامة العمليات
+اللوجستية والاحتياجات الأمنية.
+نلفت انتباهكم إلى الفقرة 3-1/1 من الشروط التعاقدية، والتي تنص على فرض
+غرامة قدرها 500 ريال يومياً عن كل جهاز أو نظام يظل العطل قائماً فيه،
+وخاصة فيما يتعلق بالأعطال التي تؤثر على خدمات أساسية مثل أنظمة مكافحة
+الحريق.
+إن أي تأخير في التنفيذ سيعرض الشركة إلى تطبيق الغرامات وفق الأحكام
+القانونية والتعاقدية المعمول بها.
+وتقبلوا تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تشمل تفاصيل قانونية إضافية (الفقرة 65 أ-10 و65 7-3-ب) وغرامات يومية محددة (500 ريال)، بينما الرد النموذجي يركز على الفقرة 3-1/1 فقط. المسودة أكثر صرامة في التحذيرات مثل 'لا يُنظر لأي ذريعة'، لكن الرد النموذجي أكثر وضوحًا في الربط بين العطل والغرامات.</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على أخطاء في اسم الشركة ('صقور العرب' بدل 'العربية')، وفقرة في التنسيق (فقرة 65 7-3-ب غير مُصاغة بشكل موحد). الرد النموذجي يستخدم علامات ترقيم صحيحة وتجنبت الأخطاء الإملائية.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:45:45</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntyD9JS9-vtkzw_cdrcgTHKPHeH-hRzp4EZD1NuGLt_4g@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">*سعادة مدير إدارة المشاريع - سلمه الله* *نفيد سعادتكم،* بحدوث خلل فني في
@@ -252,26 +323,52 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعروبة للتجارة والمقاولات المنفذة للعقد:  
-"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
-السلام عليكم ورحمة الله وبركاته:  
-بناءً على البلاغ الوارد من **مدير مركز انطلاق دوريات أمن طرق الساند**، فإن هناك **خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز**، حيث تم لحظ **تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع**، مما تسبب في **إعاقة حركة دخول وخروج دوريات أمن الطرق**، ويُعتبر هذا العطل **ثغرة أمنية مباشرة** تستدعي التدخل العاجل.  
-ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية والحركة المرورية، **نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل**، طبقًا للفقرة **65 – 7-1** من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي عطل يهدد الأداء أو السلامة.  
-كما **نحذر من أن أي تأخير في التنفيذ سي تعرض الشركة إلى غرامات تقدر بـ 500 ريال سعودي يومياً**، وفق الأنظمة الناظمة للعقود.  
+    <t>السيد/ مدير إدارة المشاريع - سلمه الله  
+السلام عليكم ورحمة الله وبركاته،
+بناءً على البلاغ الوارد من مركز انطلاق دوريات أمن طرق الساند، فقد تم الإبلاغ عن وجود خلل فني في المصدات الأمنية عند المدخل الرئيسي، حيث لوحظ تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع، مما أدى إلى إعاقة حركة دخول وخروج دوريات أمن الطرق، وبالتالي تشكل ثغرة أمنية خطيرة.
+ونظرًا لخطورة هذا العطل وتأثيره المباشر على سلامة الموقع وأمن العمليات اللوجستية، فإننا نوجهكم فورًا بتوجيه فريق فني مختص من شركة "واحة صقر لعروبة للتجارة والمقاولات" إلى الموقع لإجراء الصيانة الطارئة اللازمة، وفقًا للفقرة 65/7-3-أ من الشروط التعاقدية الخاصة بالصيانة الشهرية والطارئة، والتي تنص على وجوب التحرك الفوري في حالة حدوث أعطال طارئة.
+كما نلفت انتباهكم إلى الفقرة 65/7-3-ب من نفس الشروط، والتي توضح أنه في حالة حدوث عطل طارئ، يجب على المقاول إرسال الفنيين فورًا بعد الإبلاغ، وإعداد تقرير فني مفصل حول العطل، مع تحديد ما إذا كانت هناك حاجة إلى قطع غيار أو خدمات خاصة.
+نؤكد لكم أن أي تأخير في التنفيذ سيُعتبر مخالفة واضحة لبنود العقد، وسيتم تطبيق الغرامات وفقًا للبندين التاليين:
+- **البند 10/3**: المسؤوليات التعاقدية للشركة المنفذة، والذي يشمل التزامها بالإصلاح الفوري دون تأخير.
+- **البند 10/9**: الغرامات المالية في حالة التقصير في الالتزامات التعاقدية، والتي سيتم تطبيقها يوميًا حتى يتم حل المشكلة.
+نؤكد مرة أخرى أن هذا العطل يُعد طارئًا ويحتاج إلى تدخل فوري، ولا يُنظر لأي ذريعة تتعلق بطبيعة العطل أو مدى تعقيده، إذ أن السلامة والأمن أولوية قصوى، ولن يُسمح بأي تأخير قد يؤدي إلى تفاقم الوضع أو تعرض الموقع لخطر محتمل.
+ننتظر تأكيد توجيه فريق الصيانة إلى الموقع فورًا، وفي حال تأخر الشركة المنفذة عن الوفاء بهذا الالتزام، سيتم اتخاذ الإجراءات النظامية المناسبة، بما فيها تطبيق الغرامات ورفع الموضوع أمام الجهات المختصة.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد:  "عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  السلام عليكم ورحمة الله وبركاته:  بناءً على البلاغ الوارد من **مدير مركز انطلاق دوريات أمن طرق الساند**، فإن هناك **خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز**، حيث تم لحظ **تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر الرفع**، مما تسبب في **إعاقة حركة دخول وخروج دوريات أمن الطرق**، ويُعتبر هذا العطل **ثغرة أمنية مباشرة** تستدعي التدخل العاجل.  ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية والحركة المرورية، **نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل**، طبقًا للفقرة **65 – 7-1** من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي عطل يهدد الأداء أو السلامة.  كما نحذر من أن أي تأخير في التنفيذ سي تعرض الشركة إلى غرامات تقدر بـ 500 ريال سعودي يومياً**، وفق الأنظمة الناظمة للعقود.  وتقبلوا تحياتي  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>Error in Eval</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:38:11</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntxeUxL0T2egLEMOhbVdSkAL9UrqLq_4pNKw5SaR9JvYQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السادة شركة صقر العروبة للمقاولات العامة المنفذة للعقد:
+"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة
+الرياض (المرحلة الثالثة)"
+السلام عليكم ورحمة الله وبركاته:
+بناءً على البلاغ الوارد من مدير مركز انطلاق دوريات أمن طرق الساند، فإن
+هناك خللاً فنياً في المصدات الأمنية عند المدخل الرئيسي للمركز، حيث تم
+لوحظ تهريب في زيت الهيدروليك من البساتم وعدم استجابة المصدة لأوامر
+الرفع، مما تسبب في إعاقة حركة دخول وخروج دوريات أمن الطرق، ويُعتبر هذا
+العطل ثغرة أمنية مباشرة تستدعي التدخل العاجل.
+ونظرًا لخطورة هذا العطل وتأثيره السلبي على سلامة العمليات الأمنية
+والحركة المرورية، نشدد على ضرورة إرسال فريق فني فوري إلى الموقع لفحص
+وتحديد مصدر التهريب وإصلاح المصدات الأمنية بشكل عاجل، طبقًا للفقرة 65
+– 7-1 من الشروط التعاقدية الخاصة بإدارة الصيانة الوقائية والفنية
+للمصدات الأمنية الهيدروليكية، والتي تنص على وجوب التفاعل السريع مع أي
+عطل يهدد الأداء أو السلامة.
+كما نحذر من أن أي تأخير في التنفيذ سيتعرض الشركة إلى غرامات تقدر بـ
+500 ريال سعودي يومياً، وفق الأنظمة الناظمة للعقود.
+وتقبلوا تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تشمل تفاصيل إضافية عن البنود التعاقدية (65/7-3-أ، 65/7-3-ب، 10/3، 10/9) مقارنة بالنموذج الذي يركز على الفقرة 65-7-1 فقط. لكنها تفتقر إلى الوضوح في تحديد الغرامات (500 ريال يوميًا في النموذج مقابل ذكر البنود دون قيمة في المسودة). النموذج أكثر دقة في ربط العطل بالتأثير الأمني المباشر.</t>
+  </si>
+  <si>
+    <t>أخطاء في اسم الشركة ("واحة صقر لعروبة" بدل "صقر العروبة"). استخدام غير متسق لعلامات الترقيم (مثل الفواصل في 65/7-3-أ). جملة "لن يُسمح بأي تأخير" تفتقر إلى التناسق مع بقية النص. النموذج أكثر انتظامًا في الهيكل والعبارات.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:47:52</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuVbDmcOrQeUeKOg+5yHtJ5HgzFw4V4Nh2gDuHvnAr+qQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته :
@@ -284,62 +381,35 @@
 </t>
   </si>
   <si>
-    <t>السيد / مدير شركة واحة صقر لعرابة للتجارة والمقاولات المنفذة للعقد:  
-"عملية صيانة ونظافة وتشغيل المواقع الأمنية التابعة للأمن العام بمنطقة الرياض (المرحلة الثالثة)"  
-السلام عليكم ورحمة الله وبركاته:  
-بناءً على البلاغ الوارد من **مدير مركز شرطة البطحاء**، فإنه تم **استحداث عددٍ من المكاتب الجديدة ضمن نطاق الإدارة**، وبالتالي **توجد حاجة ملحة لتأمين الأثاث والمكاتب اللازمة لمواكبة متطلبات العمل**.  
-ونحن إذ نحيطكم علمًا بهذا الوضع، فإننا **نطالب بتوفير الأثاث اللازم بما يتوافق مع مواصفات البنية التحتية للموقع**، وذلك خلال فترة زمنية لا تتعدى الأيام الثلاثة القادمة، وبحسب الأولوية المطلوبة لضمان استمرارية العمليات الإدارية.  
-ونلفت النظر إلى أهمية الالتزام بالجدولة الزمنية المطلوبة، والتواصل المباشر مع إدارة المركز لتحديد أماكن التركيب وتفاصيل الأثاث المطلوب.  
+    <t>السيد / عقيد محمد – مدير مركز شرطة البطحاء  
+السلام عليكم ورحمة الله وبركاته:
+نحيطكم علمًا بأنه لا يمكن تزويدكم بالأثاث أو المكاتب الجديدة ضمن نطاق العقود الحالية الخاصة بصيانة ونظافة وتشغيل المواقع الأمنية، إذ إن هذه العقود لا تتضمن خدمات تركيب أو توريد الأثاث أو المعدات الإدارية.
+وعليه، يرجى التنسيق مع إدارة الإمدادات والتوريدات في الأمن العام لتلبية الحاجة المطلوبة وفق الإجراءات النظامية والموارد المالية المخصصة لهذه الغاية.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة البطحاء السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لا يقع ضمن نطاق اعمالنا .لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك .وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة تقدم تفاصيل أكثر من اللازم (مثل التواريخ والمواصفات) مقارنة بالرد النموذجي الذي اختصر المطلوب. الرد النموذجي يركز على رفض الطلب بشكل مباشر ويرجع إلى الجهة المختصة، بينما مسودة البوت تُظهر استعدادًا للتنفيذ رغم عدم توافقه مع نطاق العمل.</t>
-  </si>
-  <si>
-    <t>المسودة تستخدم الصيغة الرسمية بشكل دقيق (التحية، التهيئة، التوقيع). لا توجد أخطاء لغوية جوهرية، لكنها أطول من اللازم. الرد النموذجي أبسط وأكثر وضوحًا في التعبير.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:40:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwns7i1YT+xB9=NwX+dv760k8ScV_UUiFtF_2TW9H22L43Q@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته :
-نظرا لاستحداث مكاتب جديدة لدينا في الإدارة، آمل من سعادتكم تأمين أثاث
-ومكاتب نظرا لحاجة العمل
-وتقبلو تحياتي
-*مدير مركز شرطة البطحاء *
-*عقيد / *
-*محمد*
-</t>
-  </si>
-  <si>
-    <t>السيد / مدير مركز شرطة البطحاء  
-السلام عليكم ورحمة الله وبركاته:
-إشارة إلى إيميلكم الكريم الوارد، والمتضمن طلب تأمين أثاث ومكاتب جديدة في الإدارة، نحيط سعادتكم بأنه لا يقع موضوع الطلب ضمن نطاق اختصاص قسم الإشراف، إذ إنه يرتبط بتوفير الأثاث والمعدات الداخلية، وهي مهام تخضع لإدارة أخرى مختصة بذلك.
-لذلك، نرجو من سعادتكم مخاطبة الجهة المختصة المسؤولة عن توفير الأثاث والمعدات الإدارية، وذلك لمعالجة الطلب بما يتوافق مع الإجراءات والصلاحيات المقررة.
-وتقبلو تحياتي  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير مركز شرطة البطحاء السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لايقع ضمن نطاق اعمالنا . لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك . وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة توضح السبب بشكل دقيق (الطلب مرتبط بتوفير الأثاث والمعدات الداخلية) وتوجّه المدير إلى الجهة المختصة بشكل واضح. الرد النموذجي أقل تفصيلًا ويعتمد على عبارات مبهمة مثل 'جهة الاختصاص' دون تحديد.</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يحتوي على أخطاء إملائية (طرفكم بدل منكم) وفواصل غير مُسماة (مثل ':' بدون مسافة بعدها). المسودة تستخدم التنقيط والهياكل اللغوية بشكل دقيق.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:42:51</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsAp67zyVqmFxczcoLE8yLGhkmpvHvJoAUi2ExVW+g2xg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير مركز شرطة البطحاء
+السلام عليكم ورحمة الله وبركاته :
+إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب
+تأمين اثاث ومكاتب .
+عليه نفيد سعادتكم أن ذلك لا يقع ضمن نطاق أعمالنا .
+لذا آمل من سعادتكم مخاطبة جهة الاختصاص في ذلك .
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة أطول وتحتوي على تفاصيل إضافية عن العقود (صيانة ونظافة وتشغيل المواقع الأمنية)، بينما الرد النموذجي مباشر ومبسّط. المسودة توجّه الطرف إلى إدارة الإمدادات بشكل واضح، لكن الرد النموذجي يشير فقط إلى جهة الاختصاص دون تحديدها.</t>
+  </si>
+  <si>
+    <t>المسودة تستخدم صيغة رسمية سليمة، لكن الجملة الطويلة في الفقرة الأولى قد تُحسّن بتقسيمها. الرد النموذجي أبسط وأكثر وضوحًا في التنسيق.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:50:58</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnubTxQoi_QHWqUmCbWkWQtjXmQQWBQsUqLnYhovk2WayQ@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
@@ -352,27 +422,40 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة الخليج  
-السلام عليكم ورحمة الله وبركاته:
-إشارة إلى إيميلكم الوارد والمتضمن طلب استحداث مكاتب جديدة في الإدارة وتأمين الأثاث والمكاتب، نفيد سعادتكم بأنه **لا يقع هذا الطلب ضمن نطاق الأعمال الموكولة إلى قسم الإشراف**.
-لذلك، نأمل من سعادتكم مخاطبة الجهة المختصة بهذا النوع من الطلبات، وذلك لضمان إنهائه وفق الإجراءات النظامية.
-وتقبلو تحياتي  
+    <t>سعادة مدير مركز شرطة الخليج
+السلام عليكم ورحمة الله وبركاته:
+إشارة إلى إيميلكم الكريم المؤرخ في تاريخ 28/1/1447هـ، والذي يتضمَّن طلب تأمين أثاث ومكاتب جديدة نتيجة استحداث مكاتب في الإدارة.
+نحيط سعادتكم بأنه لا يُمكن التعامل مع هذا النوع من الطلبات ضمن نطاق مسؤوليات قسم الإشراف، إذ إن موضوع تأمين الأثاث والمكاتب يُعد من اختصاص الجهة المختصة بالإدارة المالية أو الإنشاءات أو الإمدادات، حسب نوعية الحاجة وطبيعة الاستحداث.
+لذلك، نرجو من سعادتكم التواصل المباشر مع الجهة المختصة لدراسة الطلب والتوجيه به وفق الإجراءات النظامية.
+وتقبلوا فائق التقدير والتحية،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير مركز شرطة الخليج السلام عليكم ورحمة الله وبركاته : إشارة الى ايميلكم الوارد والمتضمن استحداث مكاتب في الإدارة طرفكم وطلب تأمين اثاث ومكاتب . عليه نفيد سعادتكم ان ذلك لايقع ضمن نطاق اعمالنا. لذا امل من سعادتكم مخاطبة جهة الاختصاص في ذلك .وتقبلوا تحياتي،  مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>المسودة أضافت 'جديدة' ووضعت جملة في **الخط العريض** غير موجودة في النموذج. النموذج استخدم 'طرفكم' و'امال' بينما المسودة استخدمت 'نأمل' و'الأعمال الموكولة'. الفرق في ترتيب الجمل وتفاصيل الطلب.</t>
-  </si>
-  <si>
-    <t>المسودة صحيحة نحوًا مع فواصل وعلامات ترقيم مناسبة. النموذج يفتقر إلى فاصلة بعد 'السلام عليكم' ويستخدم 'امال' بدل 'نأمل' بشكل غير رسمي. المسودة أكثر اتساقًا في الأسلوب الرسمي.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:44:53</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuC2RgHjEpoj5rJmmE2nWvk=pmgih5MFGaP9KonVzEzJw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير مركز شرطة الخليج
+السلام عليكم ورحمة الله وبركاته:
+إشارة إلى إيميلكم الكريم المؤرخ في تاريخ 28/1/1447هـ، والذي يتضمَّن
+طلب تأمين أثاث ومكاتب جديدة نتيجة استحداث مكاتب في الإدارة.
+نحيط سعادتكم بأنه لا يُمكن التعامل مع هذا النوع من الطلبات ضمن نطاق
+مسؤوليات قسم الإشراف، إذ إن موضوع تأمين الأثاث والمكاتب يُعد من اختصاص
+الجهة المختصة بالإدارة المالية أو الإنشاءات أو الإمدادات، حسب نوعية
+الحاجة وطبيعة الاستحداث.
+لذلك، نرجو من سعادتكم التواصل المباشر مع الجهة المختصة لدراسة الطلب
+والتوجيه به وفق الإجراءات النظامية.
+وتقبلوا فائق التقدير والتحية،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تتطابق مع الرد النموذجي في المضمون والإجراءات، مع اختلاف بسيط في توزيع الفقرات (النموذج يفصل الفقرات بفواصل بينما المسودة تكتبه كنص متصل). لا توجد فروقات في المحتوى أو التوجيه الإداري.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية أو إملائية في المسودة. الصياغة متطابقة مع النموذج من حيث الأسلوب والبنية النحوية.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:53:35</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntaqW9xa=82d80OgNrSuK48MyF-=tqkfcSQBqooBpR_Kw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>INQUIRY</t>
@@ -387,78 +470,45 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة  
+    <t>سعادة مدير الإدارة العامة،  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى إيميلكم الكريم المؤرخ 2026/01/26 والمتضمن طلب معرفة ملخص البلاغات الخاصة بصيانة مركز شرطة الملز خلال اليومين الماضيين، نرفق لكم في المرفقات تقريراً مفصلاً يشمل قائمة البلاغات المسجلة، والتصرفات المتخذة بشأن كل منها، بالإضافة إلى حالة التنفيذ لكل بلاغ.  
-ونرجو أن يكون التقرير مرضياً ويحقق غرضكم الكريم.  
+إشارة إلى طلبكم الكريم حول معرفة بلاغات الصيانة التي حصلت في مركز شرطة الملز خلال اليومين الماضيين، نرفق لكم ملخصاً بذلك على النحو التالي:
+1. **بلاغ تسريبات مياه في الدور الأرضي**:  
+   - تمت متابعته فور تبلغه، وقد وجهت رسالة رسمية إلى شركة صقور العرب للمقاولات العامة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وعلاج التسريبات طبقاً للفقرة 65 أ-10 من الشروط التعاقدية، وذلك بسبب خطورة العطل وهدر المياه والتوقف الجزئي لخدمة المياه.
+2. **بلاغ خلل في المصدات الأمنية عند المدخل الرئيسي**:  
+   - تمت متابعته أيضاً فور تبلغه، ووجهت رسالة رسمية إلى نفس الشركة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وصيانة المصدات الأمنية الهيدروليكية، وفق الفقرة 65 – 7-1 من الشروط التعاقدية، نظراً لتأثيره السلبي على الحركة الأمنية والمرورية.
+3. **بلاغ تعطل مضخة الحريق في المستودع رقم (3)**:  
+   - تمت متابعته فور تبلغه، ووجهت رسالة رسمية إلى شركة صقور العرب للمقاولات العامة بتاريخ 28/1/1447هـ، لإيفاد فريق فني فوري لفحص وصيانة مضخة الحريق، وفق الفقرة 65 من الشروط التعاقدية، نظراً لخطورتها على سلامة البنية التحتية.
+وقد تم اتخاذ الإجراءات النظامية عبر التنسيق مع الشركات المختصة، مع ملاحظة عدم وجود أي تجاوب أولي حتى اللحظة، وهو ما يستدعي مزيداً من المتابعة المشددة.
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة، السلام عليكم ورحمة الله وبركاته، الإشارة إلى طلب سعادتكم بخصوص بلاغات الصيانة في مركز شرطة الملز خلال اليومين الماضيين، فإليك ملخص البلاغات والإجراءات المتخذة: بلاغ تعطل وحدات الإنارة في قاعة الاجتماعات: تم إرسال إشعار فوري إلى شركة صقور العرب للمقاولات العامة، وتم التأكيد على وجوب توجيه فريق فني لإصلاح المشكلة طبقًا للفقرة 65 من الشروط التعاقدية.  بلاغ تسريبات مياه في الدور الأرضي**: تم أيضًا إخطار نفس الشركة بإلحاح إصلاح التسريبات، وذلك وفق الفقرة 65 أ-10 من الشروط التعاقدية، مع تحذير من تطبيق الغرامات في حال التأخير. وتقبلوا تحياتي، مدير قسم الإشراف.</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى التفاصيل المحددة مثل أسماء البلاغات وشروط العقود كما في الرد النموذجي، وتكتفي بالإشارة إلى تقرير عام في المرفقات</t>
-  </si>
-  <si>
-    <t>استخدام علامة النقطة colon بعد التحيات غير مألوف (النموذج يستخدم فاصلة)، وجود تكرار في 'نرفق لكم في المرفقات' يُعتبر زائدًا</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:46:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsHBEa1oUKJ_-69czw_cUPCOmAuYQ2PhHdzU6eMQknz2Q@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*مدير قسم الاشراف*
-أتمنى أن تكون بخير. أكتب إليك اليوم بشأن مشكلة معقدة تتعلق بمشروعنا الحالي
-في بناء الهيكل المتعدد الطبقات، حيث يبدو أن هناك تداخلاً غامضاً بين العناصر
-الهيكلية والالتزامات التعاقدية. تخيل لو أننا نواجه تأخيراً غير متوقع في
-تفعيل المرحلة الأولى من التنفيذ، حيث يعتمد الاستقرار الهيكلي على توافر
-الموقع بالكامل، لكن هناك عوائق غير مرئية تحول دون ذلك، مثل اختلالات في
-الجدول الزمني الناتجة عن عوامل خارجية غير محددة بوضوح، مما يؤدي إلى إمكانية
-انهيار التوازن الإنشائي إذا لم يتم التعامل معها بطريقة استراتيجية.
-في هذا السياق، افترض أن الجهة المسؤولة قد تجاوزت الحدود الزمنية المعيارية
-لتسليم العناصر الأساسية، مما يثير تساؤلات حول الإجراءات التصحيحية الممكنة،
-خاصة إذا كان هذا التأخير يتجاوز الفترات المقبولة هندسياً، مثل تلك التي قد
-تؤدي إلى مخاطر في السلامة أو الكفاءة. هل هناك آلية غامضة للانسحاب أو إعادة
-تقييم الالتزامات دون فقدان الاستقرار الكلي للمشروع؟ هذا السيناريو يذكرني
-بمعادلات التوازن في الهندسة الإنشائية حيث يجب أن تكون القوى المتضادة
-متوازنة، لكن هنا، المتغيرات النظامية تبدو مشفرة وغير مباشرة.
-أرجو منك التفكير في هذا الأمر بعمق، ربما من خلال مراجعة الوثائق الرسمية
-المتعلقة بالالتزامات الهندسية والتعاقدية، وإخباري بأي رؤى قد تساعد في فك
-شيفرة هذه المشكلة المبهمة. هل يمكن أن يكون الحل مخفياً في فقرة معينة تتعلق
-بإدارة التأخيرات في عقود الإنشاءات؟
-مع خالص التحية، مهندس فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة المهندس فيصل المحترم،
-تحية طيبة وبعد،
-نود أن نوضح لك أنه في إطار ما ورد في رسالتك حول مشروع بناء الهيكل المتعدد الطبقات وما يرتبط به من تداخلات بين العناصر الهيكلية والالتزامات التعاقدية، فإننا نشير إلى أن النظام واضح في تحديد الإجراءات القانونية والإدارية المتعلقة بتلك الحالات.
-بناءً على ما ورد في **اللائحة المادة 133** من نظام المنافسات والمشتريات الحكومية، فإن للجهة الحكومية الحق في إنهاء العقد بالاتفاق مع المتعاقد في حال تأخرت الجهة الحكومية في تسليم موقع العمل للمقاول لمدة تزيد على المدة المحددة في الفقرة (2) من المادة (التاسعة والخمسين)، وبعد إبلاغ المتعاقد بذلك، ومضت ثلاثون يوماً دون قيام الجهة الحكومية بتسليم الموقع أو اتخاذ إجراءات مقبولة في سبيل ذلك.
-كذلك، وفي حال استمرت الجهة الحكومية في إيقاف كامل الأعمال لأسباب لا علاقة للمتعاقد بها مدة تتجاوز (180) يوماً من تاريخ خطاب الإيقاف، وبعد إبلاغ المتعاقد للجهة الحكومية لتمكينه من استئناف الأعمال، ومضت ثلاثون يوماً دون اتخاذ إجراءات مقبولة، فإن للجهة الحكومية حق إنهاء العقد بالاتفاق.
-بالإضافة إلى ذلك، نلفت النظر إلى أن **اللائحة المادة 127** تتيح تشكيل لجنة فنية لمعاينة الأعمال وإعداد محضر بالاشتراك مع المتعاقد لحصر الأعمال المنجزة ونسبة الإنجاز وتحديد أسباب ومعوقات التأخير في التنفيذ، وذلك في حال انتهت مدة العقد ولم يسلم المتعاقد الأعمال.
-أما بالنسبة لما ورد في رسالتك حول "آلية غامضة" للانسحاب أو إعادة تقييم الالتزامات دون فقدان الاستقرار الكلي للمشروع، فإننا نؤكد أن النظام لا يترك المجال للتفسير الغامض، وإنما يوفر أدوات واضحة للتعامل مع التأخيرات والتوقفات، سواء كانت بسبب الجهة الحكومية أو المقاول.
-ننوه أيضاً إلى أن **اللائحة المادة 96** تلزم الجهة الحكومية بتسليم موقع الأعمال في عقود الإنشاءات العامة خلال المدة المحددة، وإذا تأخرت، جاز للمتعاقد أن يطلب إنهاء العقد وفقاً لأحكام المادة (133).
-نأمل أن تجد في هذه المعلومات الإطار الواضح الذي يمكنك الاعتماد عليه في التعامل مع القضية، ونؤكد أن أي تأخير أو إيقاف للأعمال يستدعي إبلاغ الجهات المختصة بشكل رسمي وفوراً، مع توثيق الأسباب والإجراءات المتخذة.
-وتقبلو تحياتي  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>تحية طيبة وبعد، نحيطكم علمًا بأن التأخير في تسليم الموقع أو في إنجاز الأعمال من قبل الجهة الحكومية يُعد من الحالات التي تُنظَّم في نظام المنافسات والمشتريات الحكومية، ومن أبرز المواد المعنية: المادة 133 من اللائحة التنفيذية لنظام المنافسات والمشتريات الحكومية  تتيح للجهة الحكومية إنهاء العقد بالاتفاق مع المقاول إذا تأخرت الجهة في تسليم الموقع لمدة تزيد على المدة المحددة في الفقرة (2) من المادة (التاسعة والخمسين) من النظام، وبعد إبلاغ المقاول بذلك، ومضى (30) يومًا دون قيام الجهة بتسليم الموقع أو اتخاذ إجراءات مقبولة. كما يُمكن أيضًا إنهاء العقد إذا استمرت الجهة الحكومية في إيقاف كامل الأعمال لأسباب لا علاقة للمقاول بها مدة تتجاوز (180) يومًا. المادة 96 من اللائحة التنفيذية لنظام المنافسات والمشتريات الحكومية  تُحدد مدة تسليم الموقع من قبل الجهة الحكومية، وفي حال التأخير يُمكن للمقاول طلب إنهاء العقد وفق المادة (133) المشار إليها.الفقرة 63 من كراسة الشروط الخاصة   تجبر المقاول على الالتزام بالجدول الزمني المحدد ما لم تكن هناك أسباب خارجة عن إرادته ومقابلة بموافقة الجهة الحكومية.بناءً على ما سبق، يُمكن اتباع الآتي:  إبلاغ الجهة المسؤولة خطياً** بالتأخير المُسجَّل، وتحديد الأثر الهندسي الناتج عن هذا التأخير.طلب التفاوض على تعديل الجدول الزمني أو تعويض المقاول** وفقاً للمادة 113 من اللائحة، إذا تأثرت التكاليف أو تم تعطيل إتمام العقد.في حالة استمرار التأخير وتأثيره على السلامة أو الاستقرار الإنشائي، يُمكن **طلب إنهاء العقد بالاتفاق** وفق المادة 133 المشار إليها، مع توثيق جميع الملاحظات والمستندات الداعمة.نوصي بمراجعة وثائق العقد وكراسة الشروط الخاصة لتحديد البنود المتعلقة بإدارة التأخيرات وتحديد ما إذا كانت هناك آليات متفق عليها مسبقًا. وتقبلوا تحياتي إدارة المشاريع</t>
-  </si>
-  <si>
-    <t>المسودة تغطي المواد القانونية الأساسية (133، 127، 96) لكنها تفتقر إلى تفاصيل دقيقة مثل مدة 30 يومًا لإبلاغ الجهة الحكومية وفقرة 63 من كراسة الشروط. الرد النموذجي يقدم إرشادات عملية (إبلاغ كتابي، طلب تعديل الجدول الزمني) غير موجودة في مسودة البوت.</t>
-  </si>
-  <si>
-    <t>الترتيب غير الطبيعي في عبارة 'اللائحة المادة 133' (يجب 'المادة 133 من اللائحة'). بعض الجمل طويلة ومتكررة (مثل تكرار 'اللائحة المادة'). الرد النموذجي أكثر وضوحًا في استخدام المفردات القانونية.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:48:44</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnsj7_OA8ykQ8uKCp0+F2+G2V7qoTXo_-DXJPpV_GYMuuA@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة،
+السلام عليكم ورحمة الله وبركاته،
+إشارة إلى طلب سعادتكم بخصوص بلاغات الصيانة في مركز شرطة الملز خلال
+اليومين الماضيين، فإليك ملخص البلاغات والإجراءات المتخذة:
+بلاغ تعطل وحدات الإنارة في قاعة الاجتماعات: تم إرسال مخاطبة شركة صقور
+العرب للمقاولات العامة، وتم التأكيد على وجوب توجيه فريق فني لإصلاح
+المشكلة طبقًا للفقرة 65 من الشروط التعاقدية.
+بلاغ تسريبات مياه في الدور الأرضي: تم مخاطبة الشركة بالحاجة لإصلاح
+التسريبات، وذلك وفق الفقرة 65 أ-10 من الشروط التعاقدية، مع تحذير من
+تطبيق الغرامات في حال التأخير.
+وتقبلوا تحياتي،
+مدير قسم الإشراف.
+</t>
+  </si>
+  <si>
+    <t>المسودة أضافت بلاغاً ثالثاً (مضخة الحريق) غير موجود في الرد النموذجي، وكررت توجيه الرسائل إلى نفس الشركة في جميع البنود. الرد النموذجي كان أكثر اختصاراً وتركيزًا على البلاغات المذكورة فقط.</t>
+  </si>
+  <si>
+    <t>الاستخدام العام للغة صحيح، لكن هناك تكرارًا في عبارة 'تمت متابعته فور تبلغه' و'وجهت رسالة رسمية إلى شركة صقور العرب'، إضافة إلى تكرار ذكر التاريخ نفسه (28/1/1447هـ) في جميع البنود. الرد النموذجي كان أكثر اقتصادًا في التعبير.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:56:03</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvNLGJJMB7qGQztKTTYTmKPNsZaQLTPSRZqLs5tztR7pA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t>HR</t>
@@ -475,33 +525,42 @@
 </t>
   </si>
   <si>
-    <t>المهندس خالد محمد الصبيح  
-البسملة والتحية الرسمية  
-بناءً على ما ورد في طلبك، فقد تمت دراسة طلب الاجازة التي تتمنى الحصول عليها بتاريخ 2026/1/8 م لمدة 5 أيام، مع العلم أن المهندس سامي سيقوم بمهامك خلال تلك الفترة.  
-وقد تمت الموافقة على طلب الاجازة المشار إليه.  
+    <t>الموضوع: رد على طلب الإجازة – مهندس خالد محمد الصبيح  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم الكريم المتضمن رغبتكم في الحصول على إجازة اعتبارًا من تاريخ 8 يناير 2026م ولمدة خمسة أيام، مع ذكر أن المهندس سامي سيتولاّ مهام عملكم خلال تلك الفترة.  
+وقد تم دراسة الطلب وتقييم ظروف العمل الداخلية، ولما توفر لدينا من إمكانات لضمان استمرارية العمل بكفاءة، فقد تم **الموافقة** على طلب الإجازة المشار إليه شريطة الحرص على تسليم جميع الملفات والمهام المتعلقة بعملكم للمهندس سامي قبل بدء فترة الإجازة، وإبلاغ القسم المعني بأي تعديلات قد تطرأ.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:تحية طيبة، نود الاحاطة بطلب الموظف : مهندس / خالد محمد الصبيح اجازة اعتبارًا من تاريخ 2026/1/8 م لمدة 5 أيام، وفي تلك الفترة سيقوم المهندس / سامي بالإنابة عنه.ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة تُوَفِّق على الاجازة مباشرة دون استشارة إدارة الموارد البشرية، بينما الرد النموذجي يُبلِّغ إدارة الموارد البشرية بطلب الموظف ويُطلِب منهم اتخاذ الإجراءات. الفرق الجوهري هو عدم اتباع المسودة الإجراء الرسمي الصحيح.</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى التحيات الرسمية الكاملة (مثل 'السلام عليكم ورحمة الله')، وتستخدم تعبير 'البسملة والتحية الرسمية' غير المألوف. الرد النموذجي يحتوي على تحيات رسمية وصياغة أدق (مثل 'ارجو اكمال اللازم').</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:50:16</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvYycwA8NsGAWD+=3abgYDtd7QsMjySabYfBqipo9GMOg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف: مهندس / خالد محمد الصبيح اجازة اعتبارًا من
+تاريخ 2026/1/8 م لمدة 5 أيام، وفي تلك الفترة سيقوم المهندس / سامي
+بالإنابة عنه .
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك.
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تمنح الموافقة مباشرة بينما الرد النموذجي يطلب من إدارة الموارد البشرية اتخاذ القرار. الفرق الجوهري في الإجراء يكمن في عدم احترام سلسلة التفويض الإداري.</t>
+  </si>
+  <si>
+    <t>وجود تكرار غير ضروري في 'يتولاّ' (يجب أن يكون 'يتولا')، وخلل في تشكيل 'الإشراف' (يجب أن يكون 'الإشراف' بدون تاء مربوطة). الرد النموذجي أكثر اتساقًا في التنسيق الرسمي (كاستخدام '/' في تسمية الموظف).</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:58:04</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnt=QxPoOK=pw2_BBwTdm7wOtX07zAyk-Rxt5sQ2b1mLog@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
 نظرا لحصول ظروف شخصية اريد التقدم بطلب  اجازة من تاريخ  20/2/2026م لمدة شهر
-وحيث ان المهندس / فيصل سيقوم بمهامي خلال هذه الفترة.
+وحيث أن المهندس / فيصل سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
 مقدم الطلب :
@@ -509,64 +568,77 @@
 </t>
   </si>
   <si>
-    <t>المهندس محمد السبيعي  
-بسم الله الرحمن الرحيم  
-السلام عليكم ورحمة الله وبركاته  
-لقد تفضلتم بتقديم طلب إجازة تبدأ بتاريخ 20/2/2026م ولمدة شهر واحد، وسيقوم المهندس / فيصل بأداء مهامك خلال فترة غيابك.  
-بناءً على ذلك، سيتم تحويل طلبكم إلى إدارة الموارد البشرية للنظر فيه والتصرف حسب الأصول.  
+    <t>الموضوع: رد على طلب الاجازة – موظف / محمد السبيعي  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة اعتبارًا من التاريخ 20/2/2026م ولمدة شهر واحد، مع تحديد المهندس / فيصل ليقوم بمهمات عملكم خلال فترة غيابكم.  
+بناءً على ما ورد في الطلب، سيتم توجيه هذا الطلب إلى إدارة الموارد البشرية للنظر فيه والبت فيه وفق الأسس المعتمدة وبشكلٍ مستقل.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:تحية طيبة، نود الاحاطة بطلب الموظف :  محمد السبيعي  اجازة اعتبارًا من تاريخ 20/2/2026م لمدة شهر ، وفي تلك الفترة سيقوم المهندس / فيصل بالإنابة عنه.ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلكولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى توجيه الرسالة مباشرة لإدارة الموارد البشرية كما في النموذج، وتحتاج إلى توضيح طلب الموافقة بشكل صريح. النموذج يحتوي على بنية إجرائية أكثر اكتمالاً (مثل 'ارجو اكمال اللازم')</t>
-  </si>
-  <si>
-    <t>المسودة خالية من الأخطاء اللغوية الجسيمة، لكن استخدام 'أداء مهامك' أقل رسمية من 'الإنابة عنه' في السياق الإداري. النموذج يستخدم صيغة 'الإحاطة' بدلاً من 'تفضلتم بتقديم' لتعزيز الرسمية</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:51:59</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsMgCQWDp6PP=Ofh+y5RLmb+6arC+ePLd_qQ91_2axUWQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف : محمد السبيعي اجازة اعتبارًا من تاريخ
+20/2/2026م لمدة شهر ، وفي تلك الفترة سيقوم المهندس / فيصل بالإنابة
+عنه.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك.
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تُخاطب الموظف مباشرةً بدلًا من إدارة الموارد البشرية كما في الرد النموذجي، وتفتقر إلى طلب إجراءات محددة من الإدارة (كطلب الموافقة أو إكمال الإجراءات). الرد النموذجي يُحدد جهة العمل الأساسية (إدارة الموارد البشرية) ويُوجّه طلبًا مباشرًا.</t>
+  </si>
+  <si>
+    <t>استخدام عبارة 'البت فيه وفق الأسس المعتمدة وبشكلٍ مستقل' غير مُعبّر ويتضمن تكرارًا. العبارة 'المهندس / فيصل ليقوم بمهمات عملكم' أقل دقة من 'الإنابة عنه' في الرد النموذجي. ترتيب الجملة 'تم توجيه هذا الطلب إلى إدارة الموارد البشرية' أقل وضوحًا من 'نود الإحاطة بطلب الموظف'.</t>
+  </si>
+  <si>
+    <t>2026-01-28 16:59:41</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwnu87=wSBQkqa7qsq+VybYnsxWioG0zzGU4ozC9Bh6oUkw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة من تاريخ  20/04/2026م لمدة يومان أيام وحيث
-أن المهندس / سعد سيقوم بمهامي خلال هذه الفترة.
+ارغب في الحصول على  اجازة من تاريخ  20/04/2026م لمدة يومان أيام وحيث
+ان المهندس / سعد سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
  موظف / فهد خالد
 </t>
   </si>
   <si>
-    <t>المهندس فهد خالد  
-بسم الله الرحمن الرحيم  
-السلام عليكم ورحمة الله وبركاته  
-بناءً على ما ورد في طلبك، فقد أحيل طلب إجازتك إلى إدارة الموارد البشرية للفترات التالية:
-- اسم الموظف: فهد خالد  
-- تاريخ البدء: 20/04/2026  
-- مدة الإجازة: يومين  
-- البديل: المهندس سعد  
-وتقبلوا تحياتي، مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته:  تحية طيبة، نود الاحاطة بطلب الموظف / فهد خالد اجازة 20/04/2026م لمدة يومان ، وفي تلك الفترة سيقوم المهندس / سعد بالإنابة عنه. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ  الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى توجيه الرسالة مباشرة إلى 'مدير إدارة الموارد البشرية' كما في النموذج، وتستخدم تنسيق نقاط بدلًا من النص المنسق. النموذج يوضح طلب الموافقة بشكل أوضح ويُشير إلى إجراءات التالية (تزويد الموظف بالموافقة).</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى استخدام 'م' في التاريخ (20/04/2026م). النموذج يستخدم 'ايام' بدلًا من 'يومين' في بعض السياقات، لكن 'يومين' صحيح نحوً. المسودة تفتقر إلى التنسيق القياسي للرسائل الرسمية (مثل استخدام 'تحية طيبة' وتجنب النقاط المفردة).</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:53:42</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuCSK7jd3hR+6fKP+GuD+Y2OCC_eqdz+kO3hQDchJhf=A@mail.gmail.com&gt;</t>
+    <t>الموضوع: رد على طلب الاجازة – الموظف / فهد خالد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة مدتها يومين بدءًا من التاريخ 20/04/2026م، مع تحديد المهندس / سعد ليقوم بمهماتكم خلال فترة غيابكم.  
+وحرصاً على ضمان استمرارية العمل والتنسيق المناسب، سيتم توجيه هذا الطلب إلى إدارة الموارد البشرية للنظر فيه والتصرف عليه وفق الأنظمة المعتمدة.  
+وتقبلوا تحياتي،  
+مدير قسم الإشراف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / فهد خالد اجازة 20/04/2026م لمدة يومان ، وفي
+تلك الفترة سيقوم المهندس / سعد بالإنابة عنه.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تفتقر إلى طلب توجيه الموافقة إلى الموظف مباشرة كما في الرد النموذجي، وتغيب عن توضيح الحاجة إلى إبلاغ الموظف بعد قرار الموافقة.</t>
+  </si>
+  <si>
+    <t>استخدام 'ليقوم بمهماتكم' غير دقيق مقارنة بـ 'الإنابة عنه' في الرد النموذجي. كما أن بناء الجملة في المسودة أطول من اللازم دون ضرورة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:01:07</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnufnX2NsABSOd-zKvoLq5tkCbUBNKJp1TVirFVgneRghg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
@@ -578,98 +650,116 @@
 </t>
   </si>
   <si>
-    <t>المهندس ناصر محمد  
-البسملة والتحية الرسمية  
-تم توجيه طلبك لإدارة الموارد البشرية لاعتماد إجازتك المقدمة من تاريخ 20/04/2026م ولمدة 5 أيام، علما بأنه يُرجى تحديد البديل لأداء المهام خلال فترة غيابك في المستقبل لتتمكن الإدارة من المتابعة بشكل دقيق.
+    <t>الموضوع: رد على طلب الإجازة – الموظف ناصر محمد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن الحصول على إجازة مدتها خمسة أيام تبدأ من التاريخ 20/04/2026م. ولأنكم ذكرتم توفر بديل لتنفيذ مهامكم خلال فترة غيابكم، سيتم تحويل الطلب إلى إدارة الموارد البشرية للنظر فيه والبت فيه وفق الأنظمة النافذة.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: تحية طيبة، نود الاحاطة بطلب الموظف / ناصر محمد إجازة من تاريخ 20/04/2026م لمدة 5 ايام. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى التحيات الرسمية الكاملة (مثل 'السلام عليكم') وتغيب الإشارة إلى إبلاغ الموظف بالموافقة. الرد النموذجي يوضح الخطوات بشكل أدق (إكمال اللازم، إبلاغ الموظف).</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على تعبيرات غير مُصاغة بسلاسة مثل 'اعتماد إجازتك المقدمة من تاريخ...'، بينما الرد النموذجي أكثر انتظامًا في بناء الجمل. استخدام 'أيام' في المسودة مع حرف الجر 'لمدة' يُعتبر صحيحًا لغويًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:55:25</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntjPk1cHD8hCHA73UbANVyXmk02cmgz10eyW6sh2PWU9Q@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / ناصر محمد إجازة من تاريخ 20/04/2026م لمدة 5 ايام.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تُشير إلى تحويل الطلب إلى إدارة الموارد البشرية دون تحديد طلب واضح للرد أو الإجراء التالي، بينما الرد النموذجي يطلب مباشرةً من إدارة الموارد البشرية 'اكمل اللازم' ويرتبط بوضوح بالموافقة والرد على الموظف.</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على تكرار غير ضروري مثل 'النظر فيه والبت فيه'، وتستخدم صيغة 'البت فيه' التي تُستخدم عادةً في السياقات الرسمية لكنها أقل شيوعًا من 'البت فيه'. الرد النموذجي أكثر وضوحًا واقتصادًا في اللغة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:03:27</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwntEdykWZ87CAvETde1W_Uki2Udv7wA6xM82SPh1zzNBTg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
+احيط سعادتكم برغبتي بتقديم إجازة عرضية يوم الاحد القادم لمدة 5 أيام
+وتقبلوا تحياتي ,,
+ مهندس / فيصل
+</t>
+  </si>
+  <si>
+    <t>المكرم/ فيصل  
+السلام عليكم ورحمة الله وبركاته:
+نود إحاطتكم بأنه تم توجيه طلبكم لإدارة الموارد البشرية للاطلاع عليه والبت فيه، مع الأخذ في الاعتبار عدم ذكر الأسباب الخاصة بالإجازة في الطلب.
+وتقبلوا تحياتي،  
+مدير قسم الإشراف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نشير لطلب الموظف / م . فيصل إجازة عرضية لمدة 5 أيام ابتداء من الاحد القادم .
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تفتقر إلى تفاصيل محددة مثل نوع الإجازة ومدتها (كما في الرد النموذجي)، كما لم تطلب تأكيد الموافقة أو إكمال الإجراءات. الرد النموذجي يوضح طلب الإجازة العرضية لمدة 5 أيام ويطلب اتخاذ الإجراءات اللازمة.</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على أخطاء إملائية طفيفة مثل 'احاطتكم' (صحيح: 'إحاطتكم') وتفاوت في كتابة 'الإشراف' (النموذج: 'الاشراف'). الرد النموذجي يستخدم 'ارجو' (غير رسمي نسبيًا) بينما المسودة تستخدم 'تقبلوا تحياتي' (أرقى في الأسلوب).</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:03:42</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvjuGjqRH-mHD+4CXpyz1Z4RBp6JAshDp-wCEOiZJ7BSA@mail.gmail.com&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المكرم مدير قسم الاشراف
+السلام عليكم ورحمة الله وبركاته:
 ارغب في الحصول على  اجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
-وحيث أن المهندس / زياد سيقوم بمهامي خلال هذه الفترة.
+وحيث ان المهندس / زياد سيقوم بمهامي خلال هذه الفترة.
 ارجو الموافقة على طلب الاجازة .
 ولسعادتكم تحياتي ,,
  مهندس / حسن العريفي
 </t>
   </si>
   <si>
-    <t>المهندس حسن العريفي  
-البسملة والتحية رسمياً:
-لقد تفضلتم بلطف بتقديم طلب إجازة ابتداء من تاريخ 20/05/2026م لمدة خمسة أيام عمل، وقد أحيل الطلب إلى إدارة الموارد البشرية مع البيانات الخاصة بكم والتاريخ والمدة المشار إليهما، وسوف يُخطرنا النظام حال موافقتهم لابلاغكم فوراً.
+    <t>المهندس / حسن العريفي  
+السلام عليكم ورحمة الله وبركاته  
+لقد تم استلام طلبكم بشأن الحصول على إجازة اعتبارًا من التاريخ 20/05/2026 حتى 25/05/2026، مع العلم بأن المهندس / زياد سيقوم بمهامكم خلال فترة غيابكم.  
+وبناءً على ما ورد في الطلب، سيتم إحالة الطلب إلى إدارة الموارد البشرية للنظر فيه.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: تحية طيبة، نود الاحاطة بطلب الموظف / حسن العريفي إجازة من تاريخ 25/04/2026م وحتى 25/05/2026 م وسيقوم بالإنابة عنه المهندس / زياد. ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تفتقر إلى تفاصيل أساسية مقارنة بالنموذج: 1) عدم ذكر اسم الموظف (حسن العريفي) في النص 2) اختلاف التواريخ (20/05/2026 مقابل 25/04-25/05/2026) 3) غياب ذكر المُنيب عنه (زياد) 4) عدم توجيه الرسالة بشكل مباشر إلى إدارة الموارد البشرية 5) تعبير غير دقيق عن آلية الإبلاغ ("يُخطرنا النظام" مقابل "تزويدنا بها")</t>
-  </si>
-  <si>
-    <t>العبارات صحيحة نحوياً لكنها تفتقر إلى التوازن الرسمي: 1) استخدام "المهندس" كعنوان بدلاً من "سعادة" 2) غياب التحيات الرسمية (السلام عليكم) 3) تكرار كلمة "الإبلاغ" 4) تعبير "حال موافقتهم" غير دقيق مقارنة بـ"في حال الموافقة" 5) غياب الفواصل في الجمل الطويلة</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:57:19</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvLgQK3EgU+_7BQw0_jcaui=V7jh0_pqXWLO3cMD0+Rcw@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير إدارة الموارد البشرية
+السلام عليكم ورحمة الله وبركاته:
+نود الاحاطة بطلب الموظف / حسن العريفي إجازة من تاريخ 25/04/2026م وحتى
+25/05/2026 م وسيقوم بالإنابة عنه المهندس / زياد.
+ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا
+ابلاغ الموظف بذلك
+ولسعادتكم تحياتي
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تشير إلى إحالة الطلب إلى الموارد البشرية لكنها تفتقر إلى طلب تفاعلي (كالنموذج الذي يطلب إكمال الإجراءات وإبلاغ الموظف). الرد النموذجي يوضح تفاصيل الإجازة بشكل أكثر دقة (25/04/2026 بدلاً من 20/05/2026).</t>
+  </si>
+  <si>
+    <t>المسودة تفتقر إلى التنسيق الرسمي (مثل توجيه الرسالة مباشرة إلى الموارد البشرية). استخدام 'المهندس / حسن العريفي' كعنوان غير متوافق مع الأسلوب الرسمي. الرد النموذجي يستخدم 'نود الإحاطة' وعبارات أكثر رسمية.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:05:14</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvsYgwZMiKQwuBmKVJDG2bXLeEUsyWKK1vt=1TpCt=AiA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-احيط سعادتكم برغبتي بتقديم إجازة عرضية يوم الاحد القادم لمدة 5 أيام
-وتقبلوا تحياتي ,,
- مهندس / فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة المدير،  
-المهندس فيصل  
-السلام عليكم ورحمة الله وبركاته،  
-إحالةً لطلبكم المتضمن رغبتكم في تقديم إجازة عرضية بدءًا من يوم الأحد القادم ولمدة خمسة أيام، فإننا نقوم بإحالة الطلب إلى إدارة الموارد البشرية مع البيانات التالية:
-- اسم الموظف: المهندس فيصل  
-- تاريخ بداية الإجازة: يوم الأحد القادم  
-- مدة الإجازة: 5 أيام  
-ونرجو من إدارة الموارد البشرية إعلامنا بالموافقة عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.
-وتقبلوا تحياتي،  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير إدارة الموارد البشرية السلام عليكم ورحمة الله وبركاته: نشير لطلب الموظف / م . إجازة عرضية لمدة 5 أيام ابتداء من الاحد القادم . ارجو اكمال اللازم وفي حال الموافقة على ذلك يتم تزويدنا بها ليتسنى لنا ابلاغ الموظف بذلك ولسعادتكم تحياتي مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تشمل تفاصيل شاملة (الاسم، التاريخ، المدة) وتوجيه الطلب بشكل رسمي إلى إدارة الموارد البشرية، بينما الرد النموذجي مختصر لكنه يفتقر إلى توضيح اسم الموظف الكامل وتفاصيل أكثر رسمية.</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يحتوي على اختصار غير واضح ("م. إجازة") وعبارة "اكمل اللازم" التي تفتقر إلى الدقة. المسودة خالية من الأخطاء اللغوية وتحافظ على الأسلوب الرسمي.</t>
-  </si>
-  <si>
-    <t>2026-01-26 06:59:30</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnt0ozz=3URvOJhkbO-5QLhoVfsr-bM6H28kAsCsqaRKGQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المكرم مدير قسم الاشراف
-السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
+ارغب في الحصول على  اجازة ابتداء من تاريخ  20/05/2026م وحتى 25/05/2026 م
 وحيث انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -677,31 +767,36 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير قسم الإشراف  
-البسملة والتحية الرسمية  
-بناءً على ماورد من الفنى / عبدالmajid بشأن رغبته في الحصول على إجازة ابتداء من تاريخ 20/05/2026م حتى تاريخ 25/05/2026م، ولعدم وجود بديل عنده خلال فترة الغياب، فإننا نقوم بإحالة الطلب إلى إدارة الموارد البشرية لإكمال الإجراءات النظامية كافة، وابلاغي بالموافقه عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.  
+    <t>السيد الفنى / عبدالمجيد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم بشأن الحصول على إجازة ابتداءًا من تاريخ 20/05/2026م حتى 25/05/2026م، ولأنكم أشارتم إلى عدم توفر بديل عنكم خلال فترة غيابكم، سيتم تحويل الطلب إلى إدارة الموارد البشرية للنظر فيه والبت به وفق الأنظمة النافذة.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/5/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تشير إلى إحالة الطلب لإدارة الموارد البشرية بينما الرد النموذجي يرفض الطلب مباشرةً ويُعلِن القرار النهائي. الفرق يكمن في عدم اتخاذ قرار واضح في مسودة البوت.</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على تكرار غير ضروري (البسملة والتحية الرسمية) وعبارات غير مُنسجمة (مثل 'ابلاغي بالموافقه'). الرد النموذجي أكثر وضوحًا و Formality مُناسبة.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:00:59</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuFn=fPiCB=B5YZPM8YZW_6KjiK8r1OMagnV85D+9X_hA@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
+إشارة الى طلبكم اجازة من تاريخ 20/5/2026م وعدم توفر البديل عنكم .
+نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل.
+وتقبلوا تحياتنا،
+مدير قسم الاشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تشير إلى تحويل الطلب لإدارة الموارد البشرية للبت فيه، بينما الرد النموذجي يرفض الطلب مباشرة حتى توفر البديل. الفرق في الإجراء يعكس تباينًا في قرار الرفض المباشر مقابل التحويل للنظر.</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على تحية إضافية غير موجودة في الرد النموذجي (السيد الفنى / عبدالمجيد). كما أن استخدام 'البت به' في المسودة أقل دقة من 'البت فيه' في الرد النموذجي. بقية الجملة لغوية سليمة مع اختلاف في التعبير.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:06:30</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwntu0P-fsr6y7X6yNAjtbPh_ZBiS00ZRZchRxAtPSWVWFA@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-ارغب في الحصول على  إجازة ابتداء من تاريخ  20/04/2026م وحتى 25/05/2026 م
+ارغب في الحصول على  اجازة ابتداء من تاريخ  20/04/2026م وحتى 25/05/2026 م
 وحيث انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -709,31 +804,39 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير قسم الإشراف  
-البسملة والتحية رسمياً  
-بناءً على ماورد في رسالتكم حول طلب الإجازة من تاريخ 20/04/2026م حتى 25/05/2026م، ولعدم وجود بديل عنكم خلال فترة الغياب، سيتم إرسال الطلب إلى إدارة الموارد البشرية لإكمال الإجراءات النظامية، وسيتم إعلامكم بالموافقة عبر خطاب موجه لمدير الإدارة أو من ينوب عنه.  
+    <t>الموضوع: رد على طلب الاجازة – فني / محمد  
+السلام عليكم ورحمة الله وبركاته،  
+لقد تم استلام طلبكم المتضمن رغبتكم في الحصول على إجازة ابتداءًا من التاريخ 20/04/2026م حتى 25/05/2026م، ولأن الطلب لم يتضمن اسم البديل المسؤول عن مهامكم خلال فترة غيابكم، فإننا نرجو إعادة تقديم الطلب مع تحديد الشخص الذي سيتولاى مسؤوليات عملكم مؤقتًا.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>الفني محمد / السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/4/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة لم تُعدّد رفض الطلب بشكل مباشر كما في الرد النموذجي، بل اقتصرت على إرساله لإدارة الموارد البشرية، مما يُظهر فرقًا في القرار الإداري.</t>
-  </si>
-  <si>
-    <t>استخدام 'البسملة والتحية رسمياً' غير مألوف في الردود الرسمية، ووجود فواصل غير مُبرَّرة في التواريخ (20/04/2026م). الرد النموذجي أكثر وضوحًا في الصياغة والترابط.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:02:53</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntvKo9fxcKJp6AzPdHva1_e3g3ObP-eXC1ZFHPOWTy0iQ@mail.gmail.com&gt;</t>
+    <t xml:space="preserve"> فني / محمد
+السلام عليكم ورحمة الله وبركاته،
+لقد تم استلام طلبكم المتضمن رغبتكم في الحصول على إجازة ابتداءًا من
+التاريخ 20/04/2026م حتى 25/05/2026م، ولأن الطلب لم يتضمن اسم البديل
+المسؤول عن مهامكم خلال فترة غيابكم، فإننا نرجو إعادة تقديم الطلب مع
+تحديد الشخص الذي سيتولى مسؤوليات عملكم مؤقتًا.
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على عنوان إضافي (الموضوع: رد على طلب الاجازة – فني / محمد) غير موجود في الرد النموذجي، لكن المحتوى الأساسي متسق. الرد النموذجي يبدأ مباشرة بالاسم دون عنوان، مما يُظهر اختلافًا في التنسيق فقط.</t>
+  </si>
+  <si>
+    <t>في المسودة: 1) خطأ إملائي في 'سيتولاى' (الصحيح: سيتولى). 2) فراغ إضافي قبل الفاصلة في '2026م،' (الصحيح: 2026م،). في الرد النموذجي: التنسيق والعلامات صحيحة.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:07:49</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnsHW+u8ET5sYizSG6_T1xdHjExZYvChXpp9-51uY19wtw@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-افيدكم برغبتي  بإجازة شخصية ابتداء من تاريخ  20/03/2026م لمدة 30 يوما وحيث
+افيدكم برغبتي  باجازة شخصية ابتداء من تاريخ  20/03/2026م لمدة 30 يوما وحيث
 انه لايوجد بديل عني في فترة غيابي.
 ارجو الموافقة على طلب الاجازة ان امكن .
 ولسعادتكم تحياتي ,,
@@ -741,32 +844,40 @@
 </t>
   </si>
   <si>
-    <t>المهندس سعد
-البسملة والتحية،
-نود أن نشكرك على تقديمك للطلب، ولقد تم مراجعة طلبك بإيجاز، وقد تم تحديد أنه لا يوجد بديل عنك خلال فترة غيابك المقدرة بـ 30 يومًا ابتداءً من تاريخ 20/03/2026م، مما يستدعي رفض الطلب مؤقتًا حفاظًا على سير العمل.
-رجاءً التواصل مع إدارة الموارد البشرية لتوفير بديل خلال الفترة المشار إليها، ومن ثم إعادة تقديم الطلب بعد توفير الحل المناسب.
+    <t>الموضوع: الرد على طلب الأجازة الشخصية – المهندس / سعد  
+السلام عليكم ورحمة الله وبركاته،  
+نود إبلاغ سيادتكم بأنه لا يمكن الموافقة على طلب الأجازة الشخصية الذي تقدّمت به، وذلك بسبب عدم توفر بديل قادر على تولي مهامك خلال فترة غيابك المقدرة بـ 30 يومًا ابتداءً من التاريخ 20/03/2026م.  
+ونأمل من سيادتكم التنسيق لإيجاد حلٍّ بشأن توفير بديل مؤهل قبل تقديم الطلب مرة أخرى.  
 وتقبلوا تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>م سعد/ السلام عليكم ورحمة الله وبركاته: إشارة الى طلبكم اجازة من تاريخ 20/3/2026م وعدم توفر البديل عنكم .  نفيدكم برفض طلب الاجازة حتى وجود البديل نظرا لمصلحة العمل. وتقبلوا تحياتنا، مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة أطول وتحتوي على تفاصيل إضافية (مثل المدة 30 يومًا وطلب التواصل مع HR)، بينما الرد النموذجي أكثر اختصارًا وتركيزًا على القرار الرئيسي. المسودة توضح السبب بشكل أوضح لكنها تفتقر إلى الوضوح الموجز في الرد النموذجي.</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على تعبيرات غير مُصاغة بسلاسة مثل 'المقدرة بـ 30 يومًا' و'إعادة تقديم الطلب بعد توفير الحل المناسب'. الرد النموذجي يستخدم صيغة رسمية مختصرة (مثل 'إشارة إلى طلبكم' و'نفيدكم برفض طلب الاجازة')، بينما المسودة تفتقر إلى التناسق في الأسلوب الرسمي.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:05:31</t>
-  </si>
-  <si>
-    <t>&lt;CAN=Dwnt5rHaQiL62biVFy1L28BfH7s=1XNRHTFboe0gLnDGg0A@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">المهندس / سعد
+السلام عليكم ورحمة الله وبركاته،
+نود إبلاغ سيادتكم بأنه لا يمكن الموافقة على طلب الإجازة الشخصية الذي
+تقدّمت به، وذلك بسبب عدم توفر بديل قادر على تولي مهامك خلال فترة غيابك
+المقدرة بـ 30 يومًا ابتداءً من التاريخ 20/03/2026م.
+ونأمل منكم التنسيق لإيجاد بديل مؤهل قبل تقديم الطلب مرة أخرى.
+وتقبلوا تحياتي،
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تحتوي على عنوان إضافي غير موجود في النموذج، لكن المحتوى الأساسي مطابق. استخدام 'سيادتكم' في الفقرة الثانية غير متسق مع النموذج الذي استخدم 'منكم' بشكل أكثر مباشرة.</t>
+  </si>
+  <si>
+    <t>وجود خطأ إملائي في 'الأجازة' (يجب أن يكون 'الإجازة'). استخدام 'سيادتكم' في الفقرة الثانية غير متوافق مع الأسلوب الرسمي في النموذج.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:08:04</t>
+  </si>
+  <si>
+    <t>&lt;CAN=Dwntzg3pzX7AWgK3nLocSfa5F94Bf09jKYGkz3PuxcXSVHg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">المكرم مدير قسم الاشراف
 السلام عليكم ورحمة الله وبركاته:
-امل الافادة عاجلا هل يوجد اجازات مستقبلية للموظف:
+امل الإفادة عاجلا هل يوجد اجازات مستقبلية للموظف:
  مهندس / خالد محمد الصبيح
 وكم مدتها ومن سينوب عنه خلال تلك الفترة.
 وتقبلوا تحياتي ,
@@ -775,30 +886,42 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع  
+    <t>سعادة مدير الإدارة العامة للمشاريع،  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى طلبكم الكريم، نفيدكم بأنه لا يوجد لدى الموظف / مهندس خالد محمد الصبيح أي إجازات مستقبلية مسجلة ضمن الأنظمة الداخلية حالياً.  
+إليك الجدول التالي لأي اجازات مستقبلية للموظف **مهندس / خالد محمد الصبيح**:
+| رقم | التاريخ | المدة | البديل |
+|-----|---------|-------|--------|
+| ١ | ٠٨ يناير ٢٠٢٦ | ٥ أيام | المهندس / سامي |
+وفي حالة وجود أي تحديثات إضافية سيتم التواصل فور توفرها.
 وتقبلوا تحياتي،  
-مدير قسم الإشراف</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة / محمد،  السلام عليكم ورحمة الله وبركاته، بالإشارة إلى استفساركم حول وجود إجازات مستقبلية للمهندس / خالد محمد الصبيح: نحيطكم بأنه يوجد طلب إجازة سابقة للمهندس المذكور، وقد تم تقديمه بتاريخ 8 يناير 2025م لمدة خمسة أيام، حيث سيتولى المهندس / سامي مهامه خلال تلك الفترة. هذا الطلب قيد الدراسة ضمن الإجراءات النظامية، ولم يتم إعلان نتيجة البت فيه حتى الآن. وتقبلوا تحياتي،  إدارة المشاريع</t>
-  </si>
-  <si>
-    <t>المسودة لم تذكر تفاصيل مهمة مثل وجود طلب إجازة سابق (8 يناير 2025م)، وفترة الإجازة (5 أيام)، والمهندس البديل (سامي). الرد النموذجي أوضح الإجراءات النظامية وحالة الطلب (قيد الدراسة). المسودة كانت مختصرة بشكل مفرط.</t>
-  </si>
-  <si>
-    <t>المسودة صحيحة نحوًا لكنها أقل رسمية (مثل استخدام 'إشارة إلى' بدل 'بإحالة إلى'). الرد النموذجي استخدم ترقيمات وعبارات رسمية أكثر (مثل 'نحيطكم بأنه' وذكر اسم الإدارة). المسودة لم تذكر اسم المدير كما في النموذج.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:07:03</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnsQOO7FX=NKmWaVyMom2PhXEzLNv+CvvR2YfgywFRX5YA@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض
-السلام عليكم ورحمة الله وبركاته:
+مدير قسم الإشراف.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع،
+السلام عليكم ورحمة الله وبركاته:
+إليك الجدول التالي لأي اجازات مستقبلية للموظف **مهندس / خالد محمد الصبيح**:
+| رقم | التاريخ | المدة | البديل |
+|-----|---------|-------|--------|
+| ١ | ٠٨ يناير ٢٠٢٦ | ٥ أيام | المهندس / سامي |
+وفي حالة وجود أي تحديثات إضافية سيتم التواصل فور توفرها.
+وتقبلوا تحياتي،
+مدير قسم الإشراف.
+</t>
+  </si>
+  <si>
+    <t>الفرق الوحيد هو استخدام 'السلام عليكم ورحمة الله وبركاته:' مع علامة نصيّة (:) في مسودة البوت، بينما الرد النموذجي يستخدم علامة فاصلة (.) بعد التحيّة. باقي المحتوى متطابق.</t>
+  </si>
+  <si>
+    <t>الفرق اللغوي الوحيد هو علامة الترقيم بعد التحيّة، حيث يُستخدم عادةً النقطة (.) في الرسائل الرسمية بدلاً من النصيّة (:)، لكن هذا لا يُعد خطأً جسيمًا.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:10:57</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnuZ0Ewanf=DxwdtSHdp34jO1b9hjfwGnRt5Mk-Pp0-4bw@mail.gmail.com&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
 نظرا لطلبكم إيصال خدمة الكهرباء لمركز شرطة العريجاء.
 عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدرة 85000 ريال .
 لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
@@ -809,28 +932,42 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض  
+    <t>السيد / محمد  
+مدير فرع خدمة العملاء – الشركة السعودية للكهرباء  
 السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى إيميلكم الكريم المؤرخ 2026/01/26 والمتضمن رفع طلب ارتباط مالي بمبلغ وقدره 85,000 ريال لخدمة الكهرباء في مركز شرطة العريجاء، نشكر جهودكم في تقديم المستندات المطلوبة.  
-ونود التنويه بأن هذا الطلب لا يقع ضمن اختصاص قسم الإشراف، وإنما يتطلب إحالته إلى الجهة المالية المختصة لاتخاذ القرار المناسب بشأن الربط المالي واعتماد النفقات.  
-لذلك، نأمل من سعادتكم مخاطبة الجهة المالية المختصة لإتمام الإجراءات النظامية المتعلقة بهذا الطلب، وذلك لضمان سرعة تنفيذه.  
+إشارة إلى ماورد من سعادتكم حول طلب إيصال خدمة الكهرباء لمركز شرطة العريجاء، وما رافقه من رفع أصل طلب الارتباط المالي بمبلغ وقدره **٨٥,٠٠٠** ريال.  
+نحيط سعادتكم بأن الموضوع المشار إليه لا يدخل ضمن نطاق مسؤوليات قسم الإشراف مباشرة، وإنما يُعتبر من اختصاص الجهة المختصة في الأمور المالية والإدارية، وهي الجهة التي تقوم بتقييم الطلب واعتماده وفقاً للإجراءات النظامية والموازنات المتوفرة.  
+بناء عليه، نأمل من سعادتكم توجيه الطلب إلى الجهة المختصة في وزارة الداخلية أو الجهة المالكة للمشروع، لأخذ القرار المناسب بشأن الارتباط المالي المطلوب، ومن ثم تزويدها بأصل التعميد النهائي لمساعدتنا في إنهاء الإجراءات الفنية والتنفيذية اللازمة.  
+ونؤكد لكم أن أي تأخير في تنفيذ هذا الطلب قد يؤدي إلى تحمّل الجهات المعنية المسؤولية وفقاً للبندين التاليين من العقد:  
+- **البند (٣.٢)**: الالتزام بالتوقيت الزمني المحدد لكل مشروع أو مهمة.  
+- **البند (٧.١)**: تطبيق الغرامات المالية في حالة التأخير في التنفيذ أو عدم الالتزام بالمواعيد.  
+ونحن جاهزون للتعاون الكامل بمجرد حصولنا على التوجيه النهائي من الجهة المختصة.  
 وتقبلو تحياتي،  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة  السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير فرع خدمة العملاء بالشركة السعودية للكهرباء بشأن طلب الارتباط على مبلغ 85000 ريال لإيصال خدمة الكهرباء لمركز شرطة العريجاء  امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك . ولسعادتكم تحياتي  مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة توضح الإحالة إلى الجهة المالية بشكل عام، بينما الرد النموذجي يحدد طلب توجيه المبلغ وطلب أصل التعميد بشكل أكثر دقة. المسودة ناقصة تفاصيل مثل ذكر الجهة المحددة (الشركة السعودية للكهرباء) وطلب المستندات المطلوبة.</t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على فواصل زائدة (مثل بعد 'السلام عليكم') وعبارات غير مكتملة (مثل 'ليتنسى' في الرد النموذجي). الرد النموذجي أكثر انتظامًا في التراكيب ويعتمد على صيغة 'امل توجيه' بدلاً من 'نأمل من سعادتكم' ليعكس طلبًا مباشرًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:09:31</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntSj00awqvdb+Uf-EK4QeaesLR2WbMdaxjrR+9cZ0mNrg@mail.gmail.com&gt;</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير فرع خدمة العملاء بالشركة السعودية
+للكهرباء بشأن طلب الارتباط على مبلغ 85,000 ريال لإيصال خدمة الكهرباء
+لمركز شرطة العريجاء.
+أمل توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، وتزويدنا
+بأصل التعميد ليتمكن من إفادتهم بذلك على ضوئه.
+ولسعادتكم تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة أطول من اللازم وتحتوي على تفاصيل غير ضرورية مثل ذكر البندين (٣.٢ و٧.١) وشرح مسؤوليات الأقسام، بينما الرد النموذجي مباشر ومركز على الطلب الأساسي. المسودة لم تُراعِ التنسيق الرسمي (مثل توجيه الرد إلى 'سعادة مدير الإدارة' بوضوح).</t>
+  </si>
+  <si>
+    <t>استخدام علامات التنصيص المزدوجة (**) لتنسيق الأرقام غير متوافق مع الأعراف الرسمية. وجود فواصل زائدة بعد 'السلام عليكم...' وقبل 'بناء عليه'. الرد النموذجي أكثر نظافة في التنسيق.</t>
+  </si>
+  <si>
+    <t>2026-01-28 17:13:01</t>
+  </si>
+  <si>
+    <t>&lt;CAN=DwnvER+TaU2fKudPnozG5_4y0iy655LuOuBHMmQRS-A_HZg@mail.gmail.com&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
@@ -845,123 +982,31 @@
 </t>
   </si>
   <si>
-    <t>سعادة مدير إدارة المشاريع والصيانة بمنطقة الرياض  
-السلام عليكم ورحمة الله وبركاته:  
-إشارة إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يضمّن رفقة أصل طلب الارتباط المالي بمبلغ وقدره **٤,٨٢٠ ريالًا** لإيصال خدمة المياه لمركز شرطة الملز، نحيط سعادتكم بأن الموضوع مرتبط بإتمام إجراءات الربط المالي اللازمة لتنفيذ الخدمة.  
-ومن ثم، نأمل من سعادتكم وبعد الاطلاع على الطلب، **توجيه من ترونه مناسبًا حول الارتباط على المبلغ المذكور أعلاه، وتزويدهم بأصل التعميد** ليتسنى لنا إكمال الإجراءات النظامية بهذا الخصوص.  
+    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يتضمّن تقديم طلب ارتباط مالي بمبلغ وقدره **٤٬٨٢٠** ريالًا سعوديًا لإيصال خدمة المياه لمركز شرطة الملز.
+وعلى أساس ذلك، نأمل من سعادتكم توجيه ما ترونه مناسبًا حول الارتباط بالمبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد؛ ليتسنى لنا إعلام الجهات ذات العلاقة وإكمال الإجراءات اللازمة على ضوء ذلك.
 وتقبلو تحياتي  
 مدير قسم الإشراف</t>
   </si>
   <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 4820 ريال لإيصال خدمة المياه لمركز شرطة الملز.  امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك . ولسعادتكم تحياتي  مدير قسم الاشراف</t>
-  </si>
-  <si>
-    <t>المسودة تفوق الرد النموذجي في التفاصيل الإجرائية (مثل ذكر 'أصل التعميد' بدلاً من 'أصل التعميد ليتنسى')، وتستخدم صيغة رسمية أكثر (مثل 'تقبلو تحياتي' مقابل 'ولسعادتكم تحياتي'). الرد النموذجي يفتقر إلى التنسيق الكامل للإجراءات.</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يحتوي على خطأ إملائي في 'ليتنسى' (الصحيح: ليتسنى). المسودة خالية من الأخطاء اللغوية.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:13:02</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnvkHpmXM782+39+2_WPANBz2Cj9P5k6ygt98at83h7YAQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة الخليج .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدرة 5300  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة  
-السلام عليكم ورحمة الله وبركاته:  
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **5300 ريال** لإيصال خدمة المياه لمركز شرطة الخليج.  
-نأمل من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.  
-ولسعادتكم تحياتي،  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة السلام عليكم ورحمة الله وبركاته: نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 5300 ريال لإيصال خدمة المياه لمركز شرطة الخليج. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة تحتوي على فواصل إضافية (مثل الفاصلة بعد 'السلام عليكم') وتنسيق غير متسق (مثل استخدام **النجمة** للemphasis). الرد النموذجي أكثر اقتصاداً في الفواصل ويعتمد على التنسيق البسيط. كما أن المسودة تستخدم 'ليتسنى' بينما الرد النموذجي يكتب 'ليتنسى' (خطأ إملائي).</t>
-  </si>
-  <si>
-    <t>الرد النموذجي يحتوي على أخطاء إملائية واضحة مثل 'ليتنسى' بدل 'ليتسنى' و'اشراف' بدل 'الإشراف'. كما أن العبارة 'على ضوءه' في الرد النموذجي غير مكتملة مقارنة بـ 'على ضوء ذلك' في المسودة. المسودة تستخدم 'التفضل' بشكل صحيح بينما الرد النموذجي يحذفها.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:15:51</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwntQU4gDaSdXtMz3uWzqyREXXYY-a1zzoF8MScb71CA5Jg@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة الروضة .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدره 6000  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
-السلام عليكم ورحمة الله وبركاته:
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **6,000 ريال** لإيصال خدمة المياه لمركز شرطة الروضة.
-ونحيط سعادتكم علمًا بأن المبلغ المشار إليه مرفق بطاقة الأصل كما ورد في الإيميل، وبناءً على ذلك نرجو من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.
-وتقبلو تحياتي  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 6000 ريال لإيصال خدمة المياه لمركز شرطة الروضة. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي  مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة تشمل تفاصيل إضافية مثل التحيات والصيغة الرسمية بشكل أفضل، بينما الرد النموذجي أقصر وقليل التفاصيل. كلاهما يغطي الطلب الأساسي.</t>
-  </si>
-  <si>
-    <t>المسودة خالية من الأخطاء اللغوية. الرد النموذجي يحتوي على خطأ إملائي في 'ليتنسى' (الصحيح: ليتسنى). المسودة تستخدم صيغة صحيحة تمامًا.</t>
-  </si>
-  <si>
-    <t>2026-01-26 07:18:07</t>
-  </si>
-  <si>
-    <t>&lt;CAN=DwnuLUWixxp-Jvux2CO=W3=AO=-rndxvi-WQ4pC=95ES-mQ@mail.gmail.com&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السلام عليكم ورحمة الله وبركاته:
-نظرا لطلبكم إيصال خدمة المياه لمركز شرطة القيروان .
-عليه نرفق لسعادتكم بطيه اصل طلب الارتباط المالي بمبلغ وقدره 7000  ريال . .
-لذا امل من سعادتكم بعد الاطلاع توجيه من ترونه حيال الارتباط على المبلغ
-المالي ومن ثم تزويدنا بأصل التعميد لنمكن على ضوءه من إكمال اللازم
-وتقبلوا تحياتنا ,,
-مدير عام شركة المياه الوطنية :
-فيصل
-</t>
-  </si>
-  <si>
-    <t>سعادة مدير الإدارة العامة للمشاريع والصيانة
-السلام عليكم ورحمة الله وبركاته:
-نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ **7,000 ريال** لإيصال خدمة المياه لمركز شرطة القيروان.
-ونحيط سعادتكم علمًا بأن المبلغ المشار إليه مرفق بطاقة الأصل كما ورد في الإيميل، وبناءً على ذلك نرجو من سعادتكم توجيه ما ترونه حيال الارتباط على المبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد ليتسنى لنا على ضوء ذلك التواصل مع الجهة المرسلة والإفادة بما تم.
-وتقبلو تحياتي  
-**مدير قسم الإشراف**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة نشير للإيميل الوارد من مدير عام شركة المياه الوطنية بشأن طلب الارتباط على مبلغ 7000 ريال لإيصال خدمة المياه لمركز شرطة القيروان. امل توجيه من ترونه حيال الارتباط على المبلغ المذكور أعلاه وتزويدنا بأصل التعميد ليتنسى لنا على ضوءه افادتهم بذلك .ولسعادتكم تحياتي مدير قسم الاشراف </t>
-  </si>
-  <si>
-    <t>المسودة تغطي جميع النقاط المطلوبة (المرجع، المبلغ، طلب التوجيه، إرفاق التعميد)، لكنها أكثر تفصيلًا من الرد النموذجي. الرد النموذجي يفتقر إلى ذكر 'مرفق بطاقة الأصل' ويرتبط بعبارة 'ليتنسى' غير الدقيقة.</t>
-  </si>
-  <si>
-    <t>المسودة خالية من الأخطاء اللغوية. الرد النموذجي يحتوي على خطأ إملائي في 'ليتنسى' (الصحيح: ليتسنى) وفقرة فاصلة بعد 'امل'.</t>
+    <t xml:space="preserve">سعادة مدير الإدارة العامة للمشاريع والصيانة
+السلام عليكم ورحمة الله وبركاته:
+نشير إلى الإيميل الوارد من مدير عام شركة المياه الوطنية، والذي يتضمّن
+تقديم طلب ارتباط مالي بمبلغ وقدره **٤٬٨٢٠** ريالًا سعوديًا لإيصال خدمة
+المياه لمركز شرطة الملز.
+وعلى أساس ذلك، نأمل من سعادتكم توجيه ما ترونه مناسبًا حول الارتباط
+بالمبلغ المذكور أعلاه، والتفضل بتزويدنا بأصل التعميد؛ ليتسنى لنا إعلام
+الجهات ذات العلاقة وإكمال الإجراءات اللازمة على ضوء ذلك.
+وتقبلو تحياتي
+مدير قسم الإشراف
+</t>
+  </si>
+  <si>
+    <t>المسودة تفتقر إلى التنسيق الرسمي المطلوب (مثل فصل الفقرات بفواصل واضحة)، بينما الرد النموذجي يُظهر تنسيقًا احترافيًا مُتوافقًا مع معايير الرسائل الرسمية. الفرق بسيط في الإجراء لكنه يُظهر تفاوتًا في الجدية التنظيمية.</t>
+  </si>
+  <si>
+    <t>لا توجد أخطاء لغوية في أي من النصين. استخدام الأسلوب الرسمي والعبارات الرسمية مُحافظ عليهما في كلا النصين.</t>
   </si>
 </sst>
 </file>
@@ -982,18 +1027,12 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1023,15 +1062,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1334,10 +1369,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="11" max="11" width="170.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.2">
@@ -1362,19 +1398,19 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1400,19 +1436,19 @@
       <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>7</v>
       </c>
-      <c r="I2" s="3">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1438,28 +1474,28 @@
       <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="3">
-        <v>7</v>
-      </c>
-      <c r="I3" s="3">
-        <v>8</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>21</v>
+      <c r="L3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -1468,28 +1504,28 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="3">
+        <v>34</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
         <v>9</v>
       </c>
-      <c r="I4" s="3">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="J4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" t="s">
         <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1514,19 +1550,19 @@
       <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="3">
-        <v>8</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1552,24 +1588,28 @@
       <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3" t="s">
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
         <v>49</v>
+      </c>
+      <c r="K6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1578,36 +1618,36 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="3">
+        <v>55</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7">
         <v>9</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="J7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>21</v>
+      <c r="K7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1616,722 +1656,532 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="3">
-        <v>9</v>
-      </c>
-      <c r="I8" s="3">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>36</v>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="3">
+        <v>70</v>
+      </c>
+      <c r="H9">
         <v>7</v>
       </c>
-      <c r="I9" s="3">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="3">
-        <v>6</v>
-      </c>
-      <c r="I10" s="3">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="3">
-        <v>7</v>
-      </c>
-      <c r="I11" s="3">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="3">
-        <v>4</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="H12">
+        <v>7</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="3">
+        <v>99</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
         <v>7</v>
       </c>
-      <c r="I13" s="3">
-        <v>9</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="3" t="s">
+      <c r="J13" t="s">
         <v>100</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="K13" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H14" s="3">
-        <v>7</v>
-      </c>
-      <c r="I14" s="3">
-        <v>7</v>
-      </c>
-      <c r="J14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
         <v>107</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="3">
+        <v>113</v>
+      </c>
+      <c r="H15">
         <v>7</v>
       </c>
-      <c r="I15" s="3">
-        <v>7</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
         <v>114</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="K15" t="s">
+        <v>115</v>
+      </c>
+      <c r="L15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="3">
-        <v>4</v>
-      </c>
-      <c r="I16" s="3">
-        <v>7</v>
-      </c>
-      <c r="J16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
         <v>121</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="K16" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" s="3">
-        <v>9</v>
-      </c>
-      <c r="I17" s="3">
-        <v>10</v>
-      </c>
-      <c r="J17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="H17">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
         <v>128</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>36</v>
+      <c r="K17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
-      </c>
-      <c r="H18" s="3">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="H18">
+        <v>9</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="K18" t="s">
+        <v>136</v>
+      </c>
+      <c r="L18" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
-      </c>
-      <c r="H19" s="3">
-        <v>5</v>
-      </c>
-      <c r="I19" s="3">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19">
+        <v>9</v>
+      </c>
+      <c r="J19" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>21</v>
+      <c r="K19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" t="s">
-        <v>147</v>
-      </c>
-      <c r="H20" s="3">
+        <v>148</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
-        <v>7</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="J20" t="s">
         <v>149</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="K20" t="s">
+        <v>150</v>
+      </c>
+      <c r="L20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" s="3">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3">
-        <v>7</v>
-      </c>
-      <c r="J21" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21" t="s">
         <v>156</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="K21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" t="s">
-        <v>160</v>
-      </c>
-      <c r="G22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H22" s="3">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
-        <v>7</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>166</v>
-      </c>
-      <c r="F23" t="s">
-        <v>167</v>
-      </c>
-      <c r="G23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H23" s="3">
-        <v>9</v>
-      </c>
-      <c r="I23" s="3">
-        <v>10</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="3">
-        <v>7</v>
-      </c>
-      <c r="I24" s="3">
-        <v>6</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>180</v>
-      </c>
-      <c r="F25" t="s">
-        <v>181</v>
-      </c>
-      <c r="G25" t="s">
-        <v>182</v>
-      </c>
-      <c r="H25" s="3">
-        <v>9</v>
-      </c>
-      <c r="I25" s="3">
-        <v>10</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>185</v>
-      </c>
-      <c r="B26" t="s">
-        <v>186</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>187</v>
-      </c>
-      <c r="F26" t="s">
-        <v>188</v>
-      </c>
-      <c r="G26" t="s">
-        <v>189</v>
-      </c>
-      <c r="H26" s="3">
-        <v>9</v>
-      </c>
-      <c r="I26" s="3">
-        <v>9</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H27">
-        <f>AVERAGE(H2:H26)</f>
-        <v>6.76</v>
-      </c>
-      <c r="I27">
-        <f>AVERAGE(I2:I26)</f>
-        <v>7.32</v>
+      <c r="H22">
+        <f>AVERAGE(H2:H21)</f>
+        <v>7.05</v>
+      </c>
+      <c r="I22">
+        <f>AVERAGE(I2:I21)</f>
+        <v>7.95</v>
       </c>
     </row>
   </sheetData>
